--- a/workspaces/btc_daily_14days/ma/ma_ratio_200.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_200.xlsx
@@ -575,46 +575,46 @@
         <v>145</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.148610734002609</v>
+        <v>-2.141508408493621</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.900185120585206</v>
+        <v>-7.873278511828765</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-8.987398071586938</v>
+        <v>-8.956465799265111</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.85943540093718</v>
+        <v>-8.828888550905219</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-10.78140818652903</v>
+        <v>-10.74471406550567</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-7.724149937872355</v>
+        <v>-7.69790325639724</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-10.57382715264865</v>
+        <v>-10.53825550108028</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.971532658651171</v>
+        <v>-8.941994226162166</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.035166498102086</v>
+        <v>-9.005040195612715</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-9.197998244476089</v>
+        <v>-9.167807915721177</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-10.78850896100079</v>
+        <v>-10.75295650352841</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-12.14056065844064</v>
+        <v>-12.09982036715182</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-12.56547992219586</v>
+        <v>-12.52308128130314</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-10.24188530519066</v>
+        <v>-10.20765586570078</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>160</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.743438320210117</v>
+        <v>-3.729987514550857</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-7.857244780181752</v>
+        <v>-7.828217769084141</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.62651487951112</v>
+        <v>-2.61589232120054</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.373541861387757</v>
+        <v>-4.35657965974854</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.9137869940526</v>
+        <v>-4.895137610647573</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-5.243116069632634</v>
+        <v>-5.223591928339431</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-5.329422719271172</v>
+        <v>-5.30974458139999</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.172401264639753</v>
+        <v>-5.154057588516856</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.356034888573298</v>
+        <v>-3.343829348120266</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.329178587166588</v>
+        <v>-2.321191364947019</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.908443853593823</v>
+        <v>-1.901889828853449</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.005634733550330395</v>
+        <v>0.006043793551974375</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.297560336523411</v>
+        <v>-2.288583200799131</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.4619013277772694</v>
+        <v>0.460447582575398</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.630273019996096</v>
+        <v>1.632704364760173</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.143462482539839</v>
+        <v>4.149375087734519</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.686409976929582</v>
+        <v>1.688443948261366</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.460317282139748</v>
+        <v>6.47006639365847</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.471266999537463</v>
+        <v>7.482765892999446</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.255084861977139</v>
+        <v>7.266352607669802</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.688654858475623</v>
+        <v>7.700705422827568</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6.190084679124269</v>
+        <v>6.20004515109477</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10.26402871947997</v>
+        <v>10.28063749784922</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.931961654353316</v>
+        <v>9.948345455953586</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>10.76347088506579</v>
+        <v>10.78121535892897</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>12.86922275232421</v>
+        <v>12.89021591424134</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>12.96788184749645</v>
+        <v>12.98874173669</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>11.44231487051856</v>
+        <v>11.46109525096918</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.40918923596081</v>
+        <v>-3.554119545703301</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.989792646794314</v>
+        <v>-3.1288985517577</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.182069163648137</v>
+        <v>-3.330497365362838</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.6563515358227079</v>
+        <v>-0.692235671282404</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.453814777828399</v>
+        <v>-2.559914385250458</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.159395241759078</v>
+        <v>-4.333710035066453</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.776244823964468</v>
+        <v>-4.973391745225264</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.738594140765969</v>
+        <v>-1.802652217001373</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.536228826984413</v>
+        <v>-2.625525782025626</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.265488240468287</v>
+        <v>-4.418994815470143</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.429487347882848</v>
+        <v>-2.504789879576336</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.855812326503489</v>
+        <v>-6.074720432561698</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-6.048009525994502</v>
+        <v>-6.282594360387918</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-7.28159270264937</v>
+        <v>-7.559590585363537</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.8934383202099738</v>
+        <v>-0.8985236296003478</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-4.105011933174147</v>
+        <v>-4.124069053374768</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.699880639770733</v>
+        <v>-3.717515510463784</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.969627507163324</v>
+        <v>-3.986694501254263</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.108048722235495</v>
+        <v>-4.125811493064028</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-3.010606784519737</v>
+        <v>-3.024261402993623</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.295340501792104</v>
+        <v>-2.306038069131489</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.762523900573612</v>
+        <v>-4.781381496562609</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.003453700741233</v>
+        <v>-5.0227205739045</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-7.050393157830399</v>
+        <v>-7.077665036040869</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-8.855146482147987</v>
+        <v>-8.888844063169692</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-10.01961646274448</v>
+        <v>-10.0592801829326</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-11.63732249133835</v>
+        <v>-11.68435407098603</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-10.58900287935521</v>
+        <v>-10.63141988730412</v>
       </c>
     </row>
     <row r="11">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.3802</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3899~3912</t>
-        </is>
+      <c r="B6" t="n">
+        <v>3899</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.09057533452489963</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.3217</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3754~3767</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3754</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.01135708846057781</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.2632</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3594~3607</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3594</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.1541912888834531</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.2046</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3401~3413</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3401</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.07028860624769351</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.1461</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3139~3140</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3139</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.3728037180065868</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.08758</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2890~2890</t>
-        </is>
+      <c r="B11" t="n">
+        <v>2890</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.4823402265028278</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.02905</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2609~2609</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2609</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.9753236575592865</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 0.02948</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2418~2418</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2418</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.476785004852061</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 0.08801</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2209~2209</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2209</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>1.829784857698577</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 0.1465</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1828~1828</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1828</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1.445292533181707</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 0.2051</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1487~1487</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1487</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.4319147396420817</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 0.2636</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1273~1273</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1273</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1.55212334514745</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.3221</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1064~1064</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1064</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.735884988060697</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.3807</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>870~870</t>
-        </is>
+      <c r="B19" t="n">
+        <v>870</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.414607656801522</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.4392</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>737~737</t>
-        </is>
+      <c r="B20" t="n">
+        <v>737</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>2.323386645868716</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.4977</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>624~624</t>
-        </is>
+      <c r="B21" t="n">
+        <v>624</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>3.436048859277207</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.5563</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>550~550</t>
-        </is>
+      <c r="B22" t="n">
+        <v>550</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>3.870198043426385</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.6148</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>496~496</t>
-        </is>
+      <c r="B23" t="n">
+        <v>496</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>3.151722970112601</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.6733</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>431~431</t>
-        </is>
+      <c r="B24" t="n">
+        <v>431</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>3.423034997655456</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.7318</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>387~387</t>
-        </is>
+      <c r="B25" t="n">
+        <v>387</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>4.354106899428267</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.7904</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>348~348</t>
-        </is>
+      <c r="B26" t="n">
+        <v>348</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>4.403113403927961</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.8489</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>312~312</t>
-        </is>
+      <c r="B27" t="n">
+        <v>312</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>3.916818090046434</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.9074</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>279~279</t>
-        </is>
+      <c r="B28" t="n">
+        <v>279</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>5.212654869754182</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.966</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>240~240</t>
-        </is>
+      <c r="B29" t="n">
+        <v>240</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>3.756561679790025</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 1.024</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>198~198</t>
-        </is>
+      <c r="B30" t="n">
+        <v>198</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>3.062117235345582</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 1.083</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>175~175</t>
-        </is>
+      <c r="B31" t="n">
+        <v>175</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1.792275965504309</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 1.142</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>145~145</t>
-        </is>
+      <c r="B32" t="n">
+        <v>145</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.07964521676169767</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 1.2</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>111~111</t>
-        </is>
+      <c r="B33" t="n">
+        <v>111</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-1.142086968858628</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 1.259</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>98~98</t>
-        </is>
+      <c r="B34" t="n">
+        <v>98</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-1.473030156944667</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 1.317</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>80~80</t>
-        </is>
+      <c r="B35" t="n">
+        <v>80</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-3.743438320209975</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.3802</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>80~80</t>
-        </is>
+      <c r="B6" t="n">
+        <v>80</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>10.00656167979002</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.3217</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>225~225</t>
-        </is>
+      <c r="B7" t="n">
+        <v>225</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2.173228346456689</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.2632</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>385~385</t>
-        </is>
+      <c r="B8" t="n">
+        <v>385</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.2856461124177727</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.2046</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>578~579</t>
-        </is>
+      <c r="B9" t="n">
+        <v>578</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.3563026124325077</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.1461</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>840~852</t>
-        </is>
+      <c r="B10" t="n">
+        <v>840</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.8502458319470634</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.08758</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1089~1102</t>
-        </is>
+      <c r="B11" t="n">
+        <v>1089</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.8600444908088889</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.02905</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1370~1383</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1370</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-1.517299491576566</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 0.02948</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1561~1574</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1561</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-1.985179108011749</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 0.08801</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1770~1783</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1770</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-2.016713698785409</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 0.1465</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2151~2164</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2151</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-1.014695251818111</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 0.2051</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2492~2505</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2492</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.07826865953133222</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 0.2636</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2706~2719</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2706</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.562581387514129</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.3221</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2915~2928</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2915</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.4784109978056037</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.3807</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3109~3122</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3109</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.2512858538422691</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.4392</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3242~3255</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3242</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.3889836351101295</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.4977</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3355~3368</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3355</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.5041271563144818</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.5563</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3429~3442</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3429</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.4887898600124174</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.6148</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3483~3496</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3483</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.3195252767317172</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.6733</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3548~3561</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3548</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.2890013642987128</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.7318</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3592~3605</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3592</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.3436463645927788</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.7904</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3631~3644</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3631</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.2980486385414807</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.8489</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3667~3680</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3667</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.2108296245577961</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.9074</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3700~3713</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3700</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.271515346873052</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.966</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3739~3752</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3739</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.1213700899327961</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 1.024</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3781~3794</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3781</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.04219952210771538</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 1.083</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3804~3817</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3804</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.03472515896215356</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 1.142</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3834~3847</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3834</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.1189869462314093</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 1.2</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3868~3881</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3868</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.1476335684785113</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 1.259</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3881~3894</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3881</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.1516566977663985</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 1.317</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3899~3912</t>
-        </is>
+      <c r="B35" t="n">
+        <v>3899</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.1906107595446258</v>

--- a/workspaces/btc_daily_14days/ma/ma_ratio_200.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_200.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-200 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-200 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>145</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.141508408493621</v>
+        <v>-2.129034207516753</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.873278511828765</v>
+        <v>-7.860419269215079</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-8.956465799265111</v>
+        <v>-8.943506302136058</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.828888550905219</v>
+        <v>-8.815952577200783</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-10.74471406550567</v>
+        <v>-10.73164350573155</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-7.69790325639724</v>
+        <v>-7.684894296142666</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-10.53825550108028</v>
+        <v>-10.5252202601132</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.941994226162166</v>
+        <v>-8.92883920330582</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.005040195612715</v>
+        <v>-8.99186323980247</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-9.167807915721177</v>
+        <v>-9.154420420686435</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-10.75295650352841</v>
+        <v>-10.73951280435539</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-12.09982036715182</v>
+        <v>-12.08637737419736</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-12.52308128130314</v>
+        <v>-12.50952995149133</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-10.20765586570078</v>
+        <v>-10.21808550139893</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>160</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.729987514550857</v>
+        <v>-3.717519138278043</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-7.828217769084141</v>
+        <v>-7.815363344939442</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.61589232120054</v>
+        <v>-2.602932087330679</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.35657965974854</v>
+        <v>-4.343644439642368</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.895137610647573</v>
+        <v>-4.882066990410529</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-5.223591928339431</v>
+        <v>-5.210584692632295</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-5.30974458139999</v>
+        <v>-5.296709590577152</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.154057588516856</v>
+        <v>-5.140903331851241</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.343829348120266</v>
+        <v>-3.33065232321465</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.321191364947019</v>
+        <v>-2.307803465973393</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.901889828853449</v>
+        <v>-1.888445422174115</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.006043793551974375</v>
+        <v>0.01948772328648118</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.288583200799131</v>
+        <v>-2.275031556097488</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.460447582575398</v>
+        <v>0.4500179468775301</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.632704364760173</v>
+        <v>1.637119047984683</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.149375087734519</v>
+        <v>4.142650151611164</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.688443948261366</v>
+        <v>1.694665704317188</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.47006639365847</v>
+        <v>6.450712594395149</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.482765892999446</v>
+        <v>7.457752104146685</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.266352607669802</v>
+        <v>7.242040609760998</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.700705422827568</v>
+        <v>7.673827877929376</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6.20004515109477</v>
+        <v>6.180208743625329</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10.28063749784922</v>
+        <v>10.23880235959714</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.948345455953586</v>
+        <v>9.907465310099553</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>10.78121535892897</v>
+        <v>10.73588410399157</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>12.89021591424134</v>
+        <v>12.83412254804285</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>12.98874173669</v>
+        <v>12.93319703570764</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>11.46109525096918</v>
+        <v>11.61625506027931</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>262</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.554119545703301</v>
+        <v>-3.741458218384139</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.1288985517577</v>
+        <v>-3.323100969658476</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.330497365362838</v>
+        <v>-3.526285401578967</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.692235671282404</v>
+        <v>-0.8869465427586931</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.559914385250458</v>
+        <v>-2.756178777609854</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.333710035066453</v>
+        <v>-4.528712688325946</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.973391745225264</v>
+        <v>-5.168493168772862</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.802652217001373</v>
+        <v>-1.998879756831109</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.625525782025626</v>
+        <v>-2.61137528245672</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.418994815470143</v>
+        <v>-4.61714826174763</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.504789879576336</v>
+        <v>-2.703575800464399</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.074720432561698</v>
+        <v>-6.273524007281608</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-6.282594360387918</v>
+        <v>-6.483662850119579</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-7.559590585363537</v>
+        <v>-7.570020221061689</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>249</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.8985236296003478</v>
+        <v>-0.8860013399247251</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-4.124069053374768</v>
+        <v>-4.111159243798717</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.717515510463784</v>
+        <v>-3.704508379046182</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.986694501254263</v>
+        <v>-3.973715358855799</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.125811493064028</v>
+        <v>-4.112700688689088</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-3.024261402993623</v>
+        <v>-3.011218506699258</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.306038069131489</v>
+        <v>-2.292971814831013</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.781381496562609</v>
+        <v>-4.768200487267372</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.0227205739045</v>
+        <v>-5.230405369086178</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-7.077665036040869</v>
+        <v>-7.064259908388038</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-8.888844063169692</v>
+        <v>-8.875386769459475</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-10.0592801829326</v>
+        <v>-10.04582789421249</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-11.68435407098603</v>
+        <v>-11.67079802463443</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-10.63141988730412</v>
+        <v>-10.64184952300227</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>281</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.094861807754462</v>
+        <v>-4.08233951807884</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.859460331750746</v>
+        <v>-2.846550522174695</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.898457152226335</v>
+        <v>-2.885450020808733</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.971050994707809</v>
+        <v>-5.958071852309345</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.239009576328101</v>
+        <v>-2.225898771953162</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.009183296975344</v>
+        <v>-2.996140400680979</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.517404558731606</v>
+        <v>-4.50433830443113</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-7.119819274239092</v>
+        <v>-7.106638264943854</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.689715957574414</v>
+        <v>-4.676517218619651</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.116353598118359</v>
+        <v>-4.102948470465527</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.388722580798927</v>
+        <v>-5.375265287088709</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.642595651211579</v>
+        <v>-4.629143362491469</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.351106489914336</v>
+        <v>-4.337550443562733</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.457257043759121</v>
+        <v>-4.467686679457273</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>191</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.373019472042436</v>
+        <v>-5.360497182366814</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.319671619038104</v>
+        <v>-3.306761809462053</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.5731790690902017</v>
+        <v>-0.5601719376725995</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.08063427294138847</v>
+        <v>0.09361341533985268</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.028467570402917</v>
+        <v>-2.015356766027978</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-5.395947098655952</v>
+        <v>-5.382904202361587</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-7.051361444200488</v>
+        <v>-7.038295189900012</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-8.042105052406072</v>
+        <v>-8.028924043110834</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-10.72090598570879</v>
+        <v>-10.70770724675403</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-10.00035054246447</v>
+        <v>-9.986945414811636</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-9.681543657358084</v>
+        <v>-9.668086363647866</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-11.21784112828479</v>
+        <v>-11.20438883956468</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-10.06741511095755</v>
+        <v>-10.05385906460595</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-11.3883744069534</v>
+        <v>-11.39880404265156</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>209</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.254203870449103</v>
+        <v>-2.241681580773481</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>0.4533524218563585</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.394856202334552</v>
+        <v>3.407863333752154</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.6542959378128614</v>
+        <v>0.6672750802113256</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.986688119869882</v>
+        <v>2.999798924244821</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.284130057585436</v>
+        <v>3.297172953879802</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.199396340313157</v>
+        <v>3.212462594613633</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.775275142488475</v>
+        <v>1.788456151783713</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.714275256306287</v>
+        <v>1.72747399526105</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3856811717567226</v>
+        <v>0.3990862994095536</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.776009951603811</v>
+        <v>-0.7625526578935933</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.12918660287081</v>
+        <v>2.14263889159092</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.7519941928828402</v>
+        <v>0.7655502392344431</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.480184424680665</v>
+        <v>1.469754788982513</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>381</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.674540682414637</v>
+        <v>3.68706297209026</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.275565494647353</v>
+        <v>1.288475304223404</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.980434320859011</v>
+        <v>2.993441452276613</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.373154645067565</v>
+        <v>3.386133787466029</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.672003771202768</v>
+        <v>4.685114575577707</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.969445708918485</v>
+        <v>4.982488605212851</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8.296785482459825</v>
+        <v>8.309851736760301</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>9.404405233284741</v>
+        <v>9.417586242579979</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>9.868339730304449</v>
+        <v>9.881538469259212</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>11.64288646128709</v>
+        <v>11.65629158893992</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>12.48800190337371</v>
+        <v>12.50145919708393</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>14.09718821032538</v>
+        <v>14.11064049904549</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>15.77667113218887</v>
+        <v>15.79022717854048</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>17.07626123086936</v>
+        <v>17.06583159517121</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>341</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5.864332940787065</v>
+        <v>5.876855230462688</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.132524723717196</v>
+        <v>5.145434533293248</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9253393015781768</v>
+        <v>0.9383464329957789</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4106832256383655</v>
+        <v>-0.3977040832399013</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.242359572675412</v>
+        <v>-1.229248768300472</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.757234350502237</v>
+        <v>-4.744191454207872</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.668947539915244</v>
+        <v>-3.655881285614768</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.015896334591204</v>
+        <v>-5.002715325295966</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.7836410888087</v>
+        <v>-4.770442349853937</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.874235482047773</v>
+        <v>-3.860830354394942</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-5.252009334224589</v>
+        <v>-5.238552040514371</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.631115912949539</v>
+        <v>-4.617663624229429</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.11881920424635</v>
+        <v>-2.105263157894747</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.9893324760756315</v>
+        <v>-0.9997621117737836</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>214</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-6.231756077219266</v>
+        <v>-6.219233787543644</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-6.908750250931242</v>
+        <v>-6.89584044135519</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.434460079023161</v>
+        <v>-5.421452947605559</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.902337787537157</v>
+        <v>-3.889358645138692</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5.842628161487774</v>
+        <v>-5.829517357112834</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.8722890275104831</v>
+        <v>-0.8592461312161177</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.228050782165944</v>
+        <v>-4.214984527865468</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.826075302442817</v>
+        <v>-2.812894293147579</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.821654627877415</v>
+        <v>-3.808455888922651</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-4.671779812905342</v>
+        <v>-4.658374685252511</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.374860260251317</v>
+        <v>-4.361407971531207</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-5.262404590822392</v>
+        <v>-5.248848544470789</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-5.479972978172263</v>
+        <v>-5.490402613870415</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>209</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6166095266800298</v>
+        <v>0.6291318163556525</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.746662707974146</v>
+        <v>4.759572517550197</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.394856202334445</v>
+        <v>3.407863333752047</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.132764837334285</v>
+        <v>1.14574397973275</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.072812521783597</v>
+        <v>1.085923326158536</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.284130057585379</v>
+        <v>3.297172953879745</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.242458541270089</v>
+        <v>2.255524795570565</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.167619640096241</v>
+        <v>4.180800649391479</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.063557552957008</v>
+        <v>5.076756291911771</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>6.127307966015259</v>
+        <v>6.14071309366809</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.879492440740684</v>
+        <v>6.892949734450902</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>6.913875598086115</v>
+        <v>6.927327886806225</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.450558786184281</v>
+        <v>7.464114832535884</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.829466721331379</v>
+        <v>4.819037085633227</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>194</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.176664772573474</v>
+        <v>3.189187062249097</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.657874664763824</v>
+        <v>4.670784474339875</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>6.84032554579619</v>
+        <v>6.853332677213793</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.877795173249055</v>
+        <v>3.890774315647519</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.885765710754228</v>
+        <v>4.898876515129167</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.667743730944139</v>
+        <v>4.680786627238504</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7.160329601300674</v>
+        <v>7.17339585560115</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>8.239537955096488</v>
+        <v>8.252718964391725</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>7.147610233862643</v>
+        <v>7.160808972817406</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>6.81294896636043</v>
+        <v>6.826354094013261</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>5.061803889465565</v>
+        <v>5.075261183175783</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>5.611650964336796</v>
+        <v>5.625103253056906</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.675932435866095</v>
+        <v>4.689488482217698</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.894725933090861</v>
+        <v>3.884296297392709</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>133</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.621257869082115</v>
+        <v>-3.608735579406492</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7822061119385992</v>
+        <v>0.7951159215146504</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.891096803838202</v>
+        <v>1.904103935255804</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.021349936445702</v>
+        <v>2.034329078844166</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.482928721373575</v>
+        <v>1.496039525748515</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4.03600975683355</v>
+        <v>4.049052653127916</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.063761554423692</v>
+        <v>-2.050695300123216</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4765738437872855</v>
+        <v>0.4897548530825233</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.591944839387494</v>
+        <v>-2.578746100432731</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.690190325167293</v>
+        <v>-2.676785197514462</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.143063950236716</v>
+        <v>-2.129606656526498</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.6049213943950917</v>
+        <v>-0.5914691056749817</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.032694802332429</v>
+        <v>-4.019138755980826</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.279214071559942</v>
+        <v>-2.289643707258094</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>113</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.820871948528612</v>
+        <v>-3.80834965885299</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-5.43244556149277</v>
+        <v>-5.419535751916719</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.402535507027451</v>
+        <v>-1.389528375609849</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.272282374419952</v>
+        <v>-1.259303232021487</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-6.235482350554079</v>
+        <v>-6.22237154617914</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-5.053084660626027</v>
+        <v>-5.040041764331662</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-5.137818377898306</v>
+        <v>-5.12475212359783</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-9.144824785529366</v>
+        <v>-9.131643776234128</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-10.97573617613644</v>
+        <v>-10.96253743718168</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-10.94090560895199</v>
+        <v>-10.92750048129916</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-9.375747428844782</v>
+        <v>-9.362290135134565</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-9.341364271499351</v>
+        <v>-9.327911982779241</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-9.761618882444253</v>
+        <v>-9.74806283609265</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-10.39685330238036</v>
+        <v>-10.40728293807851</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>74</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2092643824927976</v>
+        <v>0.2217866721684203</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.300393472231171</v>
+        <v>1.313303281807222</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.445826585716766</v>
+        <v>-0.4328194542991639</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.738480600944712</v>
+        <v>3.751459743343176</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.8539946681813575</v>
+        <v>-0.8408838638064182</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.610606784519753</v>
+        <v>-4.597563888225388</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.695340501792032</v>
+        <v>-4.682274247491556</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-7.865226603276312</v>
+        <v>-7.852045593981074</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-7.926226489458692</v>
+        <v>-7.913027750503929</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-11.47905437718924</v>
+        <v>-11.46564924953641</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-11.68380770150682</v>
+        <v>-11.6703504077966</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-13.00077589551282</v>
+        <v>-12.98732360679271</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-10.71832780375494</v>
+        <v>-10.70477175740334</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-11.81995782283001</v>
+        <v>-11.83038745852816</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>54</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>10.46952464275299</v>
+        <v>10.48204693242861</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>8.857951029788623</v>
+        <v>8.870860839364674</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>6.611230471340392</v>
+        <v>6.624237602757994</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.037779900244196</v>
+        <v>3.05075904264266</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>6.203062388875516</v>
+        <v>6.216173193250455</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.796800622887368</v>
+        <v>2.809843519181733</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>6.415770609318798</v>
+        <v>6.428836863619274</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>7.800439062389351</v>
+        <v>7.813620071684589</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>9.591291028059011</v>
+        <v>9.604489767013774</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>8.74116584303097</v>
+        <v>8.754570970683801</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>6.684560666861543</v>
+        <v>6.698017960571761</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.015240120503478</v>
+        <v>3.028692409223588</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.7431336577065153</v>
+        <v>0.7566897040581182</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.9928549899828027</v>
+        <v>0.9824253542846506</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>65</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.352715525943779</v>
+        <v>1.365237815619402</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>8.971911143748841</v>
+        <v>8.984820953324892</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.730649870540148</v>
+        <v>-3.717642739122546</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.061935199470966</v>
+        <v>-2.048956057072502</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.553489739303018</v>
+        <v>3.566600543677957</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.850931677018721</v>
+        <v>3.863974573313087</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.227736421284945</v>
+        <v>2.240802675585421</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.699553136321008</v>
+        <v>1.712751875275771</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.464812566677701</v>
+        <v>5.478217694330532</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>11.41390539620627</v>
+        <v>11.42736268991649</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>16.06367316893628</v>
+        <v>16.07712545765639</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>12.56649548106834</v>
+        <v>12.58005152741994</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>11.27775527488313</v>
+        <v>11.26732563918498</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>44</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-4.766165592937249</v>
+        <v>-4.753643303261626</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-8.650466478628779</v>
+        <v>-8.637556669052728</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-15.86351700340719</v>
+        <v>-15.85050987198959</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-8.915082052617869</v>
+        <v>-8.902102910219405</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-4.908048722235556</v>
+        <v>-4.894937917860616</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.06515223906529144</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.122841316389646</v>
+        <v>2.135907570690122</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.928385190335483</v>
+        <v>3.941566199630721</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.594658031425908</v>
+        <v>1.607856770380671</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.017260119125254</v>
+        <v>3.030665246778085</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>9.630688612989488</v>
+        <v>9.644145906699706</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>14.21052631578941</v>
+        <v>14.22397860450952</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>20.60845352302638</v>
+        <v>20.62200956937798</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>16.31272030984806</v>
+        <v>16.30229067414991</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>39</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.916818090046434</v>
+        <v>3.929340379722056</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2588580870203856</v>
+        <v>-0.2459482774443345</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.910375770485665</v>
+        <v>1.923382901903267</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.604731467195506</v>
+        <v>4.617710609593971</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>6.630412816226048</v>
+        <v>6.643523620600988</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.328555502468554</v>
+        <v>-3.315512606174188</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.977391783843395</v>
+        <v>-5.964325529542919</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-6.444575182624895</v>
+        <v>-6.431394173329657</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-6.505575068807268</v>
+        <v>-6.492376329852505</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-9.919802817937686</v>
+        <v>-9.906397690284855</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-7.560453578152774</v>
+        <v>-7.546996284442557</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-12.6542755490124</v>
+        <v>-12.64082326029229</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-10.51042759585474</v>
+        <v>-10.49687154950313</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-5.132501135373325</v>
+        <v>-5.142930771071477</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>36</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>8.617672790901139</v>
+        <v>8.630195080576762</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>1.463453431957376</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-4.4998806397709</v>
+        <v>-4.486873508353298</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.369627507163166</v>
+        <v>-4.356648364764702</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-7.68582650001327</v>
+        <v>-7.672715695638331</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.9449487710357261</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.193548387096776</v>
+        <v>9.206614641397252</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.948587210537504</v>
+        <v>5.961768219832742</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.88758732435528</v>
+        <v>5.900786063310044</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.5180934162282824</v>
+        <v>-0.5046882885754513</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7.610486592787552</v>
+        <v>7.62394388649777</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.466241360978209</v>
+        <v>-3.452789072258099</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.446837361410225</v>
+        <v>4.460393407761828</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.636774639646823</v>
+        <v>-3.647204275344976</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>33</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-7.038892865664522</v>
+        <v>-7.026370575988899</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>9.136482996592811</v>
+        <v>9.149490128010413</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>18.35764522010941</v>
+        <v>18.37062436250788</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>20.84952703534036</v>
+        <v>20.8626378397153</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>15.08636291244994</v>
+        <v>15.09940580874431</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>15.00162919517759</v>
+        <v>15.01469544947807</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.473839735789937</v>
+        <v>8.487020745085175</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.412839849607721</v>
+        <v>8.426038588562484</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.532411634276855</v>
+        <v>4.545816761929686</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.32765830995919</v>
+        <v>4.341115603669408</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.698564593301356</v>
+        <v>-1.685112304581246</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.9114838260566032</v>
+        <v>0.9250398724082061</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.191508188636007</v>
+        <v>4.181078552937855</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>39</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>14.17322834645668</v>
+        <v>14.1857506361323</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>9.99755216938987</v>
+        <v>10.01046197896592</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>12.16678602689578</v>
+        <v>12.17979315831338</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.16883403129814</v>
+        <v>7.181813173696604</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>9.194515380328539</v>
+        <v>9.207626184703479</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>12.05605988214683</v>
+        <v>12.06910277844119</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>17.0995312930796</v>
+        <v>17.11259754738008</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>16.63234789429826</v>
+        <v>16.64552890359349</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>19.13545057221845</v>
+        <v>19.14864931117322</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>15.72122282308796</v>
+        <v>15.73462795074079</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>15.51646949877045</v>
+        <v>15.52992679248067</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>15.55085265611572</v>
+        <v>15.56430494483583</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>7.438290352863369</v>
+        <v>7.451846399214972</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.12390912103686</v>
+        <v>5.113479485338708</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>42</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7.03037120359955</v>
+        <v>7.042893493275173</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.037845209682942</v>
+        <v>3.050755019258993</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.023928884038767</v>
+        <v>5.036936015456369</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9.916086778550998</v>
+        <v>9.929065920949462</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>14.13957032538356</v>
+        <v>14.1526811297585</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>12.05605988214677</v>
+        <v>12.06910277844113</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>11.97132616487462</v>
+        <v>11.98439241917509</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>13.88509514704544</v>
+        <v>13.89827615634068</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>11.44314287991079</v>
+        <v>11.45634161886555</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>15.35492245678756</v>
+        <v>15.36832758444039</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.38826437056518</v>
+        <v>10.4017216642754</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.041695146958332</v>
+        <v>8.055147435678442</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>14.76429767887047</v>
+        <v>14.77785372522207</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.25211424924213</v>
+        <v>10.24168461354397</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>23</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>12.72395298413785</v>
+        <v>12.73647527381348</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.764553284216952</v>
+        <v>6.777463093793003</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>15.06533675153347</v>
+        <v>15.07834388295107</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.152111623271402</v>
+        <v>2.165090765669866</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.734135678757234</v>
+        <v>-2.721024874382294</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>14.95461060678451</v>
+        <v>14.96765350307888</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10.52205080255572</v>
+        <v>10.53511705685619</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>10.05486740377422</v>
+        <v>10.06804841306946</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>14.34169360454838</v>
+        <v>14.35489234350314</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.143742332563917</v>
+        <v>9.157147460216748</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>13.28681509520293</v>
+        <v>13.30027238891314</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>17.66902433950482</v>
+        <v>17.68247662822493</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>12.90094364160345</v>
+        <v>12.91449968795506</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>17.4984910608362</v>
+        <v>17.48806142513805</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>10.83989501312335</v>
+        <v>10.85241730279898</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>15.89498806682587</v>
+        <v>15.90789787640192</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>25.50011936022922</v>
+        <v>25.51312649164682</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>28.96370582617006</v>
+        <v>28.97668496856853</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>25.09195127776451</v>
+        <v>25.10506208213945</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>25.38939321548017</v>
+        <v>25.40243611177453</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>21.97132616487456</v>
+        <v>21.98439241917504</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>21.50414276609306</v>
+        <v>21.5173237753883</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>21.44314287991076</v>
+        <v>21.45634161886552</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>33.92635102821612</v>
+        <v>33.93975615586895</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>30.38826437056525</v>
+        <v>30.40172166427547</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>23.75598086124401</v>
+        <v>23.76943314996412</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>20.00239291696578</v>
+        <v>20.01594896331738</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>20.25211424924207</v>
+        <v>20.24168461354392</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>34</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.388914620966496</v>
+        <v>3.401436910642119</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.718517478590428</v>
+        <v>4.731427288166479</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.382472301405649</v>
+        <v>1.395479432823251</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.428451036575133</v>
+        <v>-1.415471894176669</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.797833630705682</v>
+        <v>9.810944435080621</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.212922627244879</v>
+        <v>4.225965523539244</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.069365380560832</v>
+        <v>7.082431634861308</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.602181981779331</v>
+        <v>6.615362991074569</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.482358566185262</v>
+        <v>9.495557305140025</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.749880439980913</v>
+        <v>2.763285567633744</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3960493549249477</v>
+        <v>-0.38259206121473</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>14.34421615536166</v>
+        <v>14.35766844408177</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>16.86513801500499</v>
+        <v>16.8786940613566</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>14.17368287669308</v>
+        <v>14.16325324099493</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>13</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.365237815619494</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-7.951165779328129</v>
+        <v>-7.938255969752078</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-31.42295756284775</v>
+        <v>-31.40995043143014</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5234736610094757</v>
+        <v>-0.5104945186110115</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-24.13881795300472</v>
+        <v>-24.12570714862978</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-23.84137601528906</v>
+        <v>-23.8283331189947</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-23.92610973256134</v>
+        <v>-23.91304347826086</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-32.08560082365054</v>
+        <v>-32.0724198143553</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.377369940602065</v>
+        <v>-1.364171201647302</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.227495125629943</v>
+        <v>-2.214089997977112</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.260059242360121</v>
+        <v>5.273516536070339</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.98675009201324</v>
+        <v>13.00020238073335</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>20.25880317337609</v>
+        <v>20.27235921972769</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>28.20083219796001</v>
+        <v>28.19040256226186</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>8.617672790901139</v>
+        <v>8.630195080576762</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.450543622381403</v>
+        <v>1.463453431957454</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-9.925183062718922</v>
+        <v>-9.912203920320458</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-27.13027094445771</v>
+        <v>-27.11716014008277</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-15.72171789563094</v>
+        <v>-15.70867499933657</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-15.80645161290322</v>
+        <v>-15.79338535860274</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-27.44574600897813</v>
+        <v>-27.43254727002337</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-22.74031563845055</v>
+        <v>-22.72691051079772</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-22.94506896276809</v>
+        <v>-22.93161166905787</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-28.46624136097821</v>
+        <v>-28.4527890722581</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-17.77538486081204</v>
+        <v>-17.76182881446044</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-23.08121908409127</v>
+        <v>-23.09164871978943</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-200 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-200 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3899</v>
+        <v>3900</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.09057533452489963</v>
+        <v>-0.09144503641219615</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.103477798681773</v>
+        <v>-0.1043720622484869</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.02417731496263542</v>
+        <v>-0.02509902612361259</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.007898164620470993</v>
+        <v>-0.008822277808341994</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1485809637912752</v>
+        <v>-0.1494787211350399</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.118669236529044</v>
+        <v>-0.1195700294741826</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.26625704045059</v>
+        <v>-0.2671219567314651</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.4122037981408297</v>
+        <v>-0.4130397678784732</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.3054909998706634</v>
+        <v>-0.3063557776346926</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.4497699043997727</v>
+        <v>-0.4506126965900279</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.4865007071726666</v>
+        <v>-0.4873380333929944</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3352777903837705</v>
+        <v>-0.3361537285597151</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2796583650855027</v>
+        <v>-0.2805562062972484</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3232469544853913</v>
+        <v>-0.322417950558652</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3754</v>
+        <v>3755</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.01135708846057781</v>
+        <v>-0.01276316429231628</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.196634375907017</v>
+        <v>0.1951290948780553</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.3208364917032824</v>
+        <v>0.3192868740153401</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3328167011257364</v>
+        <v>0.3312666418752528</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.2606996168556606</v>
+        <v>0.2591534742754789</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1740822106954809</v>
+        <v>0.1725663270283206</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1305036885827846</v>
+        <v>0.1289963532526528</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.08273666653105494</v>
+        <v>-0.08420064187662035</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.0305331432786673</v>
+        <v>0.02903665432651792</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1130316221297676</v>
+        <v>-0.1145135967247839</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.08995406613069434</v>
+        <v>-0.09144846167806264</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1191331509138749</v>
+        <v>0.1175832697405426</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1932495525627544</v>
+        <v>0.1916678131576361</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.05854294751945588</v>
+        <v>0.05970503076540012</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3594</v>
+        <v>3595</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1541912888834531</v>
+        <v>0.1521216634789582</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.5538898971086255</v>
+        <v>0.5516461436599229</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4515756709087952</v>
+        <v>0.4493439070655185</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.5415822597623148</v>
+        <v>0.5393294438343119</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.490230489532486</v>
+        <v>0.4879699622726292</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.4143793343030424</v>
+        <v>0.4121502388908311</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.3726961546921999</v>
+        <v>0.3704742255788744</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1430316549819395</v>
+        <v>0.140854276175105</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1807551796236382</v>
+        <v>0.1785638410877368</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.01472734865988201</v>
+        <v>-0.01689847041608061</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.009289146254324976</v>
+        <v>-0.01147085008436477</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1241677355487951</v>
+        <v>0.1219491355076272</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3037373768637863</v>
+        <v>0.3014513734026565</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.04065069888034856</v>
+        <v>0.04233366314984721</v>
       </c>
     </row>
     <row r="9">
@@ -2373,46 +2373,46 @@
         <v>3401</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.07028860624769351</v>
+        <v>0.06741437368356884</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3498532485373786</v>
+        <v>0.346807926211369</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.3813858509943486</v>
+        <v>0.3783082032528711</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.2051525514877071</v>
+        <v>0.2021320515353437</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.09341798354333264</v>
+        <v>0.09039932554120611</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.02554345022195292</v>
+        <v>0.02255931505995079</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.04315382729842554</v>
+        <v>-0.0461240127498499</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2006918395049055</v>
+        <v>-0.2036428619270296</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.3923930965943896</v>
+        <v>-0.3952927518528213</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.580111956507686</v>
+        <v>-0.5830044902396665</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.6216288608971894</v>
+        <v>-0.624521970663821</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.6002801616836777</v>
+        <v>-0.6031792508586875</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4161114444965364</v>
+        <v>-0.4190892494986045</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.6074368631758489</v>
+        <v>-0.617866498874001</v>
       </c>
     </row>
     <row r="10">
@@ -2425,46 +2425,46 @@
         <v>3139</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.3728037180065868</v>
+        <v>0.3853260076822096</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.6402109967620788</v>
+        <v>0.65312080633813</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.6912021627769533</v>
+        <v>0.7042092941945555</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2800540214990974</v>
+        <v>0.2930331638975616</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.3148812140702404</v>
+        <v>0.3279920184451797</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.389393215480176</v>
+        <v>0.4024361117745414</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.3683537657238176</v>
+        <v>0.3814200200242936</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.06698249929972633</v>
+        <v>-0.05380149000448853</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.2060022830923245</v>
+        <v>-0.2103250478011418</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2596954834117469</v>
+        <v>-0.2462903557589158</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.4644488077293261</v>
+        <v>-0.4509915140191083</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1433501358888307</v>
+        <v>-0.1298978471687207</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.07354084093307023</v>
+        <v>0.08709688728467313</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.02716790006238767</v>
+        <v>-0.03759753576053981</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>2890</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.4823402265028278</v>
+        <v>0.4948625161784506</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.050697409386323</v>
+        <v>1.063607218962375</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.071053616284537</v>
+        <v>1.084060747702139</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.6476735308989632</v>
+        <v>0.6606526732974274</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.6974876099444387</v>
+        <v>0.710598414319378</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.683510862538995</v>
+        <v>0.6965537588333603</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.5987771452667161</v>
+        <v>0.6118433995671921</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3392062032326137</v>
+        <v>0.3523872125278515</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2090021648011842</v>
+        <v>0.2222009037559474</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3277351112611413</v>
+        <v>0.3411402389139724</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2613900914418323</v>
+        <v>0.2748473851520501</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.7109981622820669</v>
+        <v>0.724450451002177</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.086591302202223</v>
+        <v>1.100147348553826</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.8864856448591354</v>
+        <v>0.8760560091609833</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>2609</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.9753236575592865</v>
+        <v>0.9878459472349093</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.471837434399554</v>
+        <v>1.484747243975605</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.498586205763864</v>
+        <v>1.511593337181466</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.360537306941701</v>
+        <v>1.373516449340165</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.013760400033583</v>
+        <v>1.026871204408522</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.08122916795238</v>
+        <v>1.094272064246745</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.149810897211339</v>
+        <v>1.162877151511815</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.142573838023552</v>
+        <v>1.155754847318789</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7366141971459683</v>
+        <v>0.7498129361007315</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.806381691305468</v>
+        <v>0.8197868189582991</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.8699303984175586</v>
+        <v>0.8833876921277763</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.287602172091084</v>
+        <v>1.301054460811194</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.672253655435171</v>
+        <v>1.685809701786773</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.462028648117752</v>
+        <v>1.451599012419599</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>2418</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.476785004852061</v>
+        <v>1.489307294527684</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.850323054418823</v>
+        <v>1.863232863994874</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.662236812669207</v>
+        <v>1.675243944086809</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.461638001521543</v>
+        <v>1.474617143920007</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.254068730204537</v>
+        <v>1.267179534579476</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.592867160889604</v>
+        <v>1.605910057183969</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.79762889440309</v>
+        <v>1.810695148703566</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.868079904223741</v>
+        <v>1.881260913518979</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.641654046163858</v>
+        <v>1.654852785118621</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.660015213493253</v>
+        <v>1.673420341146084</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.703400846992054</v>
+        <v>1.716858140702271</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.275418412939629</v>
+        <v>2.288870701659739</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.599580675443853</v>
+        <v>2.613136721795456</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.477093570995578</v>
+        <v>2.466663935297426</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>2209</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.829784857698577</v>
+        <v>1.8423071473742</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.983715998016351</v>
+        <v>1.996625807592402</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.498308586123244</v>
+        <v>1.511315717540846</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.538023013434227</v>
+        <v>1.551002155832691</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.090140503658574</v>
+        <v>1.103251308033514</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.432851794022497</v>
+        <v>1.445894690316862</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.665003545288016</v>
+        <v>1.678069799588492</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.87686043623038</v>
+        <v>1.890041445525618</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.634783139455045</v>
+        <v>1.647981878409809</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.780583712688781</v>
+        <v>1.793988840341612</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.937985209557255</v>
+        <v>1.951442503267472</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.289253835440483</v>
+        <v>2.302706124160594</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.774386277460728</v>
+        <v>2.787942323812331</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.571414083254439</v>
+        <v>2.560984447556287</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>1828</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.445292533181707</v>
+        <v>1.45781482285733</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.131311918029262</v>
+        <v>2.144221727605313</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.189397259572729</v>
+        <v>1.202404390990331</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.155536606622242</v>
+        <v>1.168515749020706</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.3435924156200869</v>
+        <v>0.3567032199950262</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6957389485217433</v>
+        <v>0.7087818448161087</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2827776601334975</v>
+        <v>0.2958439144339735</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3079356180259438</v>
+        <v>0.3211166273211816</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.08129183927232475</v>
+        <v>-0.06809310031756155</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.274961882068304</v>
+        <v>-0.2615567544154729</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.2608968256419004</v>
+        <v>-0.2474395319316827</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1718090731104738</v>
+        <v>-0.1583567843903637</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.06439145817657277</v>
+        <v>0.07794750452817567</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.4517515421510794</v>
+        <v>-0.4621811778492315</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>1487</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.4319147396420817</v>
+        <v>0.4444370293177045</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.44307145620035</v>
+        <v>1.455981265776401</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.249951236490105</v>
+        <v>1.262958367907707</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.514703360355171</v>
+        <v>1.527682502753635</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.707284162767877</v>
+        <v>0.7203949671428163</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.94621903928649</v>
+        <v>1.959261935580855</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.188990365726383</v>
+        <v>1.202056620026859</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.528800914490269</v>
+        <v>1.541981923785507</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9970545589064983</v>
+        <v>1.010253297861262</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5504263476512676</v>
+        <v>0.5638314753040987</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.8836689883639437</v>
+        <v>0.8971262820741615</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.8508026500805954</v>
+        <v>0.8642549388007055</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.5650470303932593</v>
+        <v>0.5786030767448622</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.3284730630197643</v>
+        <v>-0.3389026987179165</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>1273</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.55212334514745</v>
+        <v>1.564645634823073</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.847069763605035</v>
+        <v>2.859979573181086</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.373646461564611</v>
+        <v>2.386653592982213</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.425344998728271</v>
+        <v>2.438324141126735</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.808369188212268</v>
+        <v>1.821479992587207</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.420029507703262</v>
+        <v>2.433072403997627</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.099632004099483</v>
+        <v>2.112698258399959</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.260885368868649</v>
+        <v>2.274066378163887</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.807112505467181</v>
+        <v>1.820311244421944</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.428314893102254</v>
+        <v>1.441720020755085</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.087662118666842</v>
+        <v>2.101119412377059</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.729272298793113</v>
+        <v>1.742724587513223</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.544681474179711</v>
+        <v>1.558237520531314</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.5375292793546649</v>
+        <v>0.5270996436565127</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>1064</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.735884988060697</v>
+        <v>1.74840727773632</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.473935435246815</v>
+        <v>2.486845244822867</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.173051691056244</v>
+        <v>2.186058822473846</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.679244673287805</v>
+        <v>2.692223815686269</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.952853533403612</v>
+        <v>1.965964337778551</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.250295471119273</v>
+        <v>2.263338367413638</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.071576791440975</v>
+        <v>2.084643045741451</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.886348279877517</v>
+        <v>1.899529289172754</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.167453656853112</v>
+        <v>1.180652395807876</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.5052983966372082</v>
+        <v>0.5187035242900393</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.146409733973769</v>
+        <v>1.159867027683987</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.7108680792891278</v>
+        <v>0.7243203680092378</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.3845984307502377</v>
+        <v>0.3981544771018406</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.3055298610336266</v>
+        <v>-0.3159594967317787</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>870</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.414607656801522</v>
+        <v>1.427129946477145</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.986942089814278</v>
+        <v>1.999851899390329</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.132303268275152</v>
+        <v>1.145310399692754</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.411981688238974</v>
+        <v>2.424960830637438</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.298847829488651</v>
+        <v>1.31195863386359</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.711232295939936</v>
+        <v>1.724275192234302</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.936843406253864</v>
+        <v>0.94990966055434</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4696600074723634</v>
+        <v>0.4828410167676012</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1660525223880924</v>
+        <v>-0.1528537834333292</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.9012351786803947</v>
+        <v>-0.8878300510275636</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2733218418296204</v>
+        <v>0.2867791355398381</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3819501732387494</v>
+        <v>-0.3684978845186393</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.5723197267123794</v>
+        <v>-0.5587636803607765</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.242138624321157</v>
+        <v>-1.252568260019309</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>737</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.323386645868716</v>
+        <v>2.335908935544339</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.2043503463373</v>
+        <v>2.217260155913351</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9953703778682552</v>
+        <v>1.008377509285857</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.482475613596513</v>
+        <v>2.495454755994977</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.265628346963965</v>
+        <v>1.278739151338904</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.291699864055474</v>
+        <v>1.304742760349839</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.478336567407347</v>
+        <v>1.491402821707823</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.4684123273775427</v>
+        <v>0.4815933366727805</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2717272308831653</v>
+        <v>0.2849259698379285</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5783979541447621</v>
+        <v>-0.5649928264919311</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.7093860349704926</v>
+        <v>0.7228433286807103</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.3417124901806829</v>
+        <v>-0.3282602014605729</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.05214416074687023</v>
+        <v>0.06570020709847313</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.0549866100976</v>
+        <v>-1.065416245795753</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>624</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.436048859277207</v>
+        <v>3.44857114895283</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.587295759133454</v>
+        <v>3.600205568709505</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.42960653971636</v>
+        <v>1.442613671133962</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.162423774887955</v>
+        <v>3.175402917286419</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.624002559815786</v>
+        <v>2.637113364190725</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.44067526676222</v>
+        <v>2.453718163056585</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.676454370002759</v>
+        <v>2.689520624303235</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.209270971221258</v>
+        <v>2.222451980516496</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.308527495295365</v>
+        <v>2.321726234250129</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.298145900011029</v>
+        <v>1.31155102766386</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.53570026800115</v>
+        <v>2.549157561711368</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.28803214329529</v>
+        <v>1.3014844320154</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.829315993888855</v>
+        <v>1.842872040240458</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.6367296338574491</v>
+        <v>0.6262999981592969</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>550</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.870198043426385</v>
+        <v>3.882720333102007</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.894988066825761</v>
+        <v>3.907897876401812</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.681937542047358</v>
+        <v>1.69494467346496</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.084917947382138</v>
+        <v>3.097897089780602</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.091951277764501</v>
+        <v>3.10506208213944</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.389393215480162</v>
+        <v>3.402436111774527</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.66829586184425</v>
+        <v>3.681362116144726</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.564748826699116</v>
+        <v>3.577929835994354</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.685567122335001</v>
+        <v>3.698765861289765</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.017260119125254</v>
+        <v>3.030665246778085</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.448870431171308</v>
+        <v>4.462327724881526</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.210526315789473</v>
+        <v>3.223978604509583</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.51754443211729</v>
+        <v>3.531100478468893</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.312720309848125</v>
+        <v>2.302290674149972</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>496</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.151722970112601</v>
+        <v>3.164245259788224</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.354665486180608</v>
+        <v>3.367575295756659</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.145280650551754</v>
+        <v>1.158287781969356</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.090049912191517</v>
+        <v>3.103029054589982</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.753241600345156</v>
+        <v>2.766352404720095</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.453909344512432</v>
+        <v>3.466952240806798</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.369175627240153</v>
+        <v>3.382241881540629</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.103605131684454</v>
+        <v>3.116786140979691</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.042605245502152</v>
+        <v>3.055803984456915</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.394092963700032</v>
+        <v>2.407498091352863</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.205468671640517</v>
+        <v>4.218925965350735</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.231787312856909</v>
+        <v>3.245239601577019</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.819597218041046</v>
+        <v>3.833153264392649</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.456415324510886</v>
+        <v>2.445985688812733</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>431</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.423034997655456</v>
+        <v>3.435557287331079</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.507517069145955</v>
+        <v>2.520426878722006</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.880629801064444</v>
+        <v>1.893636932482046</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.867031425551289</v>
+        <v>3.880010567949753</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.632554526024364</v>
+        <v>2.645665330399304</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.394033586709867</v>
+        <v>3.407076483004232</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.541318430922502</v>
+        <v>3.554384685222978</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.842116470656087</v>
+        <v>2.855297479951325</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.245153707443627</v>
+        <v>3.258352446398391</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.930991399445858</v>
+        <v>1.944396527098689</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.11834944403779</v>
+        <v>3.131806737748008</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.296584109503868</v>
+        <v>1.310036398223978</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.500459428953405</v>
+        <v>2.514015475305008</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.126050830835254</v>
+        <v>1.115621195137102</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>387</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.354106899428267</v>
+        <v>4.36662918910389</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.776125017730159</v>
+        <v>3.78903482730621</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.898052176766647</v>
+        <v>3.91105930818425</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.320294973456825</v>
+        <v>5.333274115855289</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.489884094301978</v>
+        <v>3.502994898676917</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.787326032017639</v>
+        <v>3.800368928312004</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.70259231474536</v>
+        <v>3.715658569045836</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.718613050330781</v>
+        <v>2.731794059626019</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.432806962598093</v>
+        <v>3.446005701552856</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.807487979120552</v>
+        <v>1.820893106773383</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.377928453252586</v>
+        <v>2.391385746962804</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.1716677175673595</v>
+        <v>-0.1582154288472495</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.4416694027538952</v>
+        <v>0.4552254491054981</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.6005989290525093</v>
+        <v>-0.6110285647506615</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>348</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.403113403927961</v>
+        <v>4.415635693603583</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>4.241231209735155</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.120809015401584</v>
+        <v>4.133816146819186</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.40048743536542</v>
+        <v>5.413466577763884</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.13792828925876</v>
+        <v>3.151039093633699</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.584795514330743</v>
+        <v>4.597838410625108</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.787418118897548</v>
+        <v>4.800484373198024</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.745522076437879</v>
+        <v>3.758703085733117</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.54659115577283</v>
+        <v>4.559789894727594</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.121753327066735</v>
+        <v>3.135158454719566</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.491712646427324</v>
+        <v>3.505169940137542</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.227245229060102</v>
+        <v>1.240697517780212</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.669059583632446</v>
+        <v>1.682615629984049</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.09271333696483453</v>
+        <v>-0.1031429726629867</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>312</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.916818090046434</v>
+        <v>3.929340379722056</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.548834220671921</v>
+        <v>4.561744030247972</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.115503975613791</v>
+        <v>5.128511107031393</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.527808390272568</v>
+        <v>6.540787532671033</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.386823072636304</v>
+        <v>4.399933877011243</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.004777830864782</v>
+        <v>5.017820727159148</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4.279018472566868</v>
+        <v>4.292084726867344</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.491322253272543</v>
+        <v>3.504503262567781</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.391860828628701</v>
+        <v>4.405059567583464</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.541735643600774</v>
+        <v>3.555140771253605</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.016469498770377</v>
+        <v>3.029926792480595</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.76880137406453</v>
+        <v>1.78225366278464</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.348546763119629</v>
+        <v>1.362102809471232</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.3162168133446244</v>
+        <v>0.3057871776464722</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>279</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.212654869754182</v>
+        <v>5.225177159429805</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.601081256789925</v>
+        <v>3.613991066365976</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.639904306465738</v>
+        <v>4.65291143788334</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.128580378141329</v>
+        <v>5.141559520539793</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.43962152866056</v>
+        <v>2.452732333035499</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.812332283580524</v>
+        <v>3.825375179874889</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.010752688172047</v>
+        <v>3.023818942472523</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.901992228458653</v>
+        <v>2.915173237753891</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.916261159480648</v>
+        <v>3.929459898435411</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.424558913520812</v>
+        <v>3.437964041173643</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.861382650135141</v>
+        <v>2.874839943845359</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.178919929344367</v>
+        <v>2.192372218064477</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.400242379331374</v>
+        <v>1.413798425682977</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.1421509837328472</v>
+        <v>-0.1525806194309993</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>240</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.756561679790025</v>
+        <v>3.769083969465647</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.561654733492432</v>
+        <v>2.574564543068483</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.416786026895849</v>
+        <v>3.429793158313451</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.797039159503342</v>
+        <v>4.810018301901806</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.341951277764508</v>
+        <v>1.355062082139447</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.472726548813498</v>
+        <v>2.485769445107863</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.7213261648745615</v>
+        <v>0.7343924191750375</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.6708094327597252</v>
+        <v>0.683990442054963</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.443142879910752</v>
+        <v>1.456341618865515</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.426351028216153</v>
+        <v>1.439756155868984</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.8049310372319098</v>
+        <v>0.8183883309421276</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.005980861244012203</v>
+        <v>0.01943314996412226</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.4190595836324391</v>
+        <v>0.432615629984042</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.9978857507579306</v>
+        <v>-1.008315386456083</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>198</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.074639525021205</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.460644632482328</v>
+        <v>2.473554442058379</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.075876935986756</v>
+        <v>3.088884067404358</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.711180573644754</v>
+        <v>3.724159716043218</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.372695186881955</v>
+        <v>-1.359584382507016</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.4398982659852209</v>
+        <v>0.4529411622795863</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.665037471489079</v>
+        <v>-1.651971217188603</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.132220870270579</v>
+        <v>-2.119039860975342</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6780692413013725</v>
+        <v>-0.6648705023466093</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.5281944263293</v>
+        <v>-1.514789298676469</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.227897245596367</v>
+        <v>-1.214439951886149</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.698564593301448</v>
+        <v>-1.685112304581338</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.623869709296848</v>
+        <v>-2.610313662945245</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.384249387121571</v>
+        <v>-3.394679022819723</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>175</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.792275965504309</v>
+        <v>1.804798255179932</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.894988066825775</v>
+        <v>1.907897876401826</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.500119360229185</v>
+        <v>1.513126491646787</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.916086778550962</v>
+        <v>3.929065920949427</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.193763007949777</v>
+        <v>-1.180652203574837</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.467749641662685</v>
+        <v>-1.45470674536832</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.266769073220686</v>
+        <v>-3.25370281892021</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-3.733952472002187</v>
+        <v>-3.720771462706949</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.652095215327343</v>
+        <v>-2.63889647637258</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.930791828926694</v>
+        <v>-2.917386701273863</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-3.135545153244273</v>
+        <v>-3.122087859534055</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-4.244019138755988</v>
+        <v>-4.230566850035878</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-4.664273749700889</v>
+        <v>-4.650717703349287</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-6.12883813171031</v>
+        <v>-6.139267767408462</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>145</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.07964521676169767</v>
+        <v>-0.06712292708607492</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.001563657312168</v>
+        <v>-0.9886538477361171</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-3.465397881150132</v>
+        <v>-3.45239074973253</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.266179231301258</v>
+        <v>-1.253200088902794</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-6.632186653269976</v>
+        <v>-6.619075848895037</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-7.024399887968109</v>
+        <v>-7.011356991673743</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-8.488443950067975</v>
+        <v>-8.475377695767499</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-8.955627348849475</v>
+        <v>-8.942446339554238</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7.63731689020419</v>
+        <v>-7.624118151249426</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-10.55640759247349</v>
+        <v>-10.54300246482066</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-10.07150574437728</v>
+        <v>-10.05804845066707</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-10.03712258703185</v>
+        <v>-10.02367029831174</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-9.767722025562961</v>
+        <v>-9.754165979211358</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-11.58696621052805</v>
+        <v>-11.5973958462262</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>111</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.142086968858628</v>
+        <v>-1.129564679183005</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.753660581822885</v>
+        <v>-2.740750772246834</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.950331090221276</v>
+        <v>-4.937323958803674</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.216474354010167</v>
+        <v>-1.203495211611703</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-11.66480547899225</v>
+        <v>-11.65169467461731</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-10.46646264037569</v>
+        <v>-10.45341974408132</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-13.25389906035067</v>
+        <v>-13.24083280605019</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-13.72108245913217</v>
+        <v>-13.70790144983693</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-12.88118144441357</v>
+        <v>-12.86798270545881</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-14.6322075303424</v>
+        <v>-14.61880240268957</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-13.03515905285818</v>
+        <v>-13.02170175914796</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-17.50528040001725</v>
+        <v>-17.49182811129714</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-17.92553501096215</v>
+        <v>-17.91197896461055</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-19.47761548048766</v>
+        <v>-19.48804511618582</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>98</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.473030156944667</v>
+        <v>-1.460507867269044</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.064195606643615</v>
+        <v>-2.051285797067564</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.438656149974904</v>
+        <v>-1.425649018557301</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.308403017367404</v>
+        <v>-1.29542387496894</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.01008953856202</v>
+        <v>-9.996978734187081</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.692239437581051</v>
+        <v>-8.679196541286686</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-11.83819764464926</v>
+        <v>-11.82513139034878</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-11.28497288016545</v>
+        <v>-11.27179187087021</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-14.40719725614367</v>
+        <v>-14.3939985171889</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-16.2777306044369</v>
+        <v>-16.26432547678407</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-15.46207576548917</v>
+        <v>-15.44861847177896</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-21.55014158773558</v>
+        <v>-21.53668929901547</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-22.99080436194579</v>
+        <v>-22.97724831559419</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-25.80230751946542</v>
+        <v>-25.81273715516357</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>80</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-3.743438320209975</v>
+        <v>-3.730916030534353</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-2.855011933174239</v>
+        <v>-2.842102123598188</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.7498806397708222</v>
+        <v>-0.7368735083532201</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.6303724928366847</v>
+        <v>0.6433516352351489</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-6.158048722235492</v>
+        <v>-6.144937917860553</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-7.110606784519831</v>
+        <v>-7.097563888225466</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-10.94534050179211</v>
+        <v>-10.93227424749163</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-12.66252390057361</v>
+        <v>-12.64934289127837</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-11.47352378675591</v>
+        <v>-11.46032504780115</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-14.82364897178384</v>
+        <v>-14.81024384413101</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-13.77840229610142</v>
+        <v>-13.7649450023912</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-19.99401913875599</v>
+        <v>-19.98056685003588</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-24.16427374970089</v>
+        <v>-24.15071770334929</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-26.4145524174246</v>
+        <v>-26.42498205312275</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-200 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-200 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>80</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.00656167979002</v>
+        <v>10.01908396946565</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.394988066825768</v>
+        <v>8.407897876401819</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.000119360229178</v>
+        <v>8.01312649164678</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>13.13037249283668</v>
+        <v>13.14335163523514</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12.59195127776451</v>
+        <v>12.60506208213945</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.38939321548017</v>
+        <v>10.40243611177453</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.30465949820789</v>
+        <v>10.31772575250837</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.587476099426382</v>
+        <v>8.60065710872162</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.776476213244088</v>
+        <v>9.789674952198851</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>15.17635102821616</v>
+        <v>15.18975615586899</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>17.47159770389858</v>
+        <v>17.4850549976088</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>15.00598086124401</v>
+        <v>15.01943314996412</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>17.08572625029911</v>
+        <v>17.09928229665071</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>17.3354475825754</v>
+        <v>17.32501794687725</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>225</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.173228346456689</v>
+        <v>2.185750636132312</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.105011933174232</v>
+        <v>-2.092102123598181</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.944325084215265</v>
+        <v>-2.931317952797663</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.036294173829987</v>
+        <v>-1.023315031431522</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2.463604277791042</v>
+        <v>-2.450493473416103</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.277273451186495</v>
+        <v>-1.26423055489213</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.139784946236553</v>
+        <v>-3.126718691936077</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.718079456129161</v>
+        <v>-2.704898446833923</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.334634897867026</v>
+        <v>-2.321436158912263</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5180934162282824</v>
+        <v>-0.5046882885754513</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.7228467405458616</v>
+        <v>-0.7093894468356439</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-2.466241360978209</v>
+        <v>-2.452789072258099</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.997607083034225</v>
+        <v>-1.984051036682622</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.4145524174245949</v>
+        <v>-0.4249820531227471</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>385</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2856461124177727</v>
+        <v>-0.27312382274215</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.494622322784622</v>
+        <v>-4.481712513208571</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.811568951459137</v>
+        <v>-2.798561820041535</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.421575559111382</v>
+        <v>-2.408596416712918</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.479477293664068</v>
+        <v>-3.466366489289129</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.922295096208146</v>
+        <v>-2.90925219991378</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.045989852441465</v>
+        <v>-4.032923598140989</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.733952472002187</v>
+        <v>-3.720771462706949</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.755991319223448</v>
+        <v>-2.742792580268684</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.268454166589038</v>
+        <v>-1.255049038936207</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.213467231166355</v>
+        <v>-1.200009937456137</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.438824333561186</v>
+        <v>-1.425372044841076</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.11881920424635</v>
+        <v>-2.105263157894747</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.05091605378824227</v>
+        <v>-0.06134568948639441</v>
       </c>
     </row>
     <row r="9">
@@ -4064,49 +4064,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3563026124325077</v>
+        <v>0.3688249021081305</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.600694143882343</v>
+        <v>-1.587784334306292</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.304716563777724</v>
+        <v>-1.291709432360122</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.5526522855827878</v>
+        <v>0.565631427981252</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1869426421859259</v>
+        <v>0.2000534465608652</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.4843845799015867</v>
+        <v>0.4974274761959521</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1184838523966008</v>
+        <v>-0.1054175980961247</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.4129556795028009</v>
+        <v>-0.3997746702075631</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.598583294418525</v>
+        <v>1.611782033373288</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.475573826143616</v>
+        <v>2.488978953796448</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.788955216851946</v>
+        <v>2.802412510562164</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.341473089223285</v>
+        <v>3.354925377943395</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.921218478278384</v>
+        <v>2.934774524629987</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.793060039322803</v>
+        <v>3.851356461557728</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.8502458319470634</v>
+        <v>-0.8982665580841811</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.048607702856955</v>
+        <v>-2.096796959278933</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.911645345653177</v>
+        <v>-1.960434025392004</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1651192537318451</v>
+        <v>0.1139398705292578</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.6627657033675618</v>
+        <v>-0.7135480474247515</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.009662274484413</v>
+        <v>-1.059828039168863</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.622054449782652</v>
+        <v>-1.671648509593169</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.8429972733546691</v>
+        <v>-0.8940237423422062</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2794347931257448</v>
+        <v>0.292633532080508</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.3244552936190104</v>
+        <v>0.2711171026145465</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.135595331419346</v>
+        <v>1.081026561589844</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.4068122151632494</v>
+        <v>0.3530630432025532</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.05391887812312746</v>
+        <v>0.0001136505699506074</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.2521142492420623</v>
+        <v>0.2932105747012628</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.8600444908088889</v>
+        <v>-0.8943339815769704</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.515547809650165</v>
+        <v>-2.549452395830485</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.318062457952635</v>
+        <v>-2.352450256763753</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.7754509830504901</v>
+        <v>-0.8111938193103185</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.4472108351681</v>
+        <v>-1.482745015221788</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.465666037026665</v>
+        <v>-1.501024726112533</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.775632472595035</v>
+        <v>-1.810806608476135</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.737866366327033</v>
+        <v>-1.773430482519252</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.9273629092421984</v>
+        <v>-0.9637497053353954</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.361846593009815</v>
+        <v>-1.398452253637409</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.150197167896287</v>
+        <v>-1.187177390314346</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.981874317491098</v>
+        <v>-2.018112637581666</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.627576501994469</v>
+        <v>-2.663549967327285</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.236407330188605</v>
+        <v>-2.204798566884229</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.517299491576566</v>
+        <v>-1.541609672152852</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.585475030135157</v>
+        <v>-2.609817235673383</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.436158699148081</v>
+        <v>-2.460824304301127</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.833395623105353</v>
+        <v>-1.858458647168916</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.608556336448686</v>
+        <v>-1.634068352643155</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.780418105274549</v>
+        <v>-1.805685715636628</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.335137161196606</v>
+        <v>-2.360068151700631</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.836942505224769</v>
+        <v>-2.861761191931961</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.696251059483188</v>
+        <v>-1.721952954777898</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.925177356063308</v>
+        <v>-1.951152935040099</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.017659397339578</v>
+        <v>-2.043693182886109</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.526817972575223</v>
+        <v>-2.552489646831212</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.980831007177187</v>
+        <v>-3.006402834544623</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.691924680198319</v>
+        <v>-2.66859985035105</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.985179108011749</v>
+        <v>-2.004725554343878</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.674624139150076</v>
+        <v>-2.694389290053074</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.209804303892959</v>
+        <v>-2.230039433337332</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.600690524349822</v>
+        <v>-1.621279408021856</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.659641078923393</v>
+        <v>-1.680424868847183</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.220549423143154</v>
+        <v>-2.240875990136296</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.909626216077818</v>
+        <v>-2.929565515815412</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.4713943536687</v>
+        <v>-3.491179625972251</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.796959291225896</v>
+        <v>-2.817217198407398</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.910709674659238</v>
+        <v>-2.931252784105467</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.953594111958196</v>
+        <v>-2.974210178110049</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.588868786868595</v>
+        <v>-3.609083474076797</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.847372341250185</v>
+        <v>-3.867608298358881</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.75600020730289</v>
+        <v>-3.736121617783439</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.016713698785409</v>
+        <v>-2.032485537260811</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.309276804105764</v>
+        <v>-2.325416761848317</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.552098494908392</v>
+        <v>-1.568803923616969</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.335919641994778</v>
+        <v>-1.352717988571705</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.113782280414242</v>
+        <v>-1.130892974040329</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.573486424564827</v>
+        <v>-1.590256412115288</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.191119905281134</v>
+        <v>-2.207583583824587</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.853965342015051</v>
+        <v>-2.870220775352657</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.265777307882679</v>
+        <v>-2.282397119873217</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.522352466710565</v>
+        <v>-2.539117083567632</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.696902014093517</v>
+        <v>-2.713648497317926</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.914448032661177</v>
+        <v>-2.931074464249072</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.304589955234484</v>
+        <v>-3.321146597254476</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.137716259232512</v>
+        <v>-3.121763532512922</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.014695251818111</v>
+        <v>-1.025950672566687</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.677827467154813</v>
+        <v>-1.689144637461403</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.7533496499465855</v>
+        <v>-0.7651906604567884</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5056756330309824</v>
+        <v>-0.5176104369202648</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.09323390742067517</v>
+        <v>-0.1054885888461996</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4188513421854196</v>
+        <v>-0.4308972215588014</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.3394554230154654</v>
+        <v>-0.3515655860743081</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.6887176882416668</v>
+        <v>-0.7007794065703052</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1214829704293905</v>
+        <v>-0.1338299156731892</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.01796451702745827</v>
+        <v>-0.03055924301783364</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.01099282534932655</v>
+        <v>-0.02364569844688447</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.09597157188033378</v>
+        <v>0.08326787605511754</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.07364446591249418</v>
+        <v>0.06084755443055201</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.44272326830297</v>
+        <v>0.4523413669516003</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.07826865953133222</v>
+        <v>-0.08666223963251696</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.7503793453148049</v>
+        <v>-0.7587687902648454</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5246509154400272</v>
+        <v>-0.5331993869474729</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.492729025948293</v>
+        <v>-0.5012748130269387</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2499119769336176</v>
+        <v>-0.2586469506343363</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.01060678451983</v>
+        <v>-1.018995315654493</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.7937798775424127</v>
+        <v>-0.8022742474916384</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.27941741538546</v>
+        <v>-1.287798273431235</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.7581653566397719</v>
+        <v>-0.7667702039260504</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.5448028179376863</v>
+        <v>-0.5536359146155903</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.727300091692598</v>
+        <v>-0.7360988485450477</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.5503543432467666</v>
+        <v>-0.5592241646651388</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.2262472755733356</v>
+        <v>-0.2353207506628365</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.2467637944534076</v>
+        <v>0.2537183078880716</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2706</v>
+        <v>2707</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.562581387514129</v>
+        <v>-0.5691513246519975</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.235254758781295</v>
+        <v>-1.241789508666223</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.9113638933593364</v>
+        <v>-0.9180729196850805</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7613800844829086</v>
+        <v>-0.7681316183533724</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.6907374883496686</v>
+        <v>-0.6975888751506858</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.9997003733186531</v>
+        <v>-1.006403667230991</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.06467334366458</v>
+        <v>-1.071367836290456</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.401461953670953</v>
+        <v>-1.408097037979438</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.9999900353726545</v>
+        <v>-1.006785224792296</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.8706969422635495</v>
+        <v>-0.8776543937436969</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.16581462537421</v>
+        <v>-1.172694079881978</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.8525863470277741</v>
+        <v>-0.8595812464921337</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.6243771852383873</v>
+        <v>-0.6315153399814832</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2061266968037572</v>
+        <v>-0.2003791717042134</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4784109978056037</v>
+        <v>-0.4836473381478754</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.808120918483425</v>
+        <v>-0.8134135990080154</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.603776743666927</v>
+        <v>-0.6091830402971894</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6260377635735708</v>
+        <v>-0.6314262184900841</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5646834691575151</v>
+        <v>-0.5701515930742289</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6933984369317372</v>
+        <v>-0.6987950783759516</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.8281262649680201</v>
+        <v>-0.8334887531365212</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.002989494548274</v>
+        <v>-1.008343575741065</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.565989540180567</v>
+        <v>-0.5715027266782471</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3696407497900083</v>
+        <v>-0.3753123372816987</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.5895743317422628</v>
+        <v>-0.5951950880369736</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.296127469232502</v>
+        <v>-0.301848549830261</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.0456180569711222</v>
+        <v>-0.05147190286933778</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1549158501568755</v>
+        <v>0.1593800867949469</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.2512858538422691</v>
+        <v>-0.2554917590005701</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.4683570148788121</v>
+        <v>-0.472627427890302</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1409062807964645</v>
+        <v>-0.1453163151459194</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.3459019541014499</v>
+        <v>-0.3502381083546027</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.2255599473798142</v>
+        <v>-0.2299812009641116</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3597245259378639</v>
+        <v>-0.3640808863011529</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3307705403030283</v>
+        <v>-0.3351455981493174</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.427371412612132</v>
+        <v>-0.4317562417276619</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.08543772381436554</v>
+        <v>-0.08993981505636839</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.07797325757690032</v>
+        <v>0.07334639350546723</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.2372711907029625</v>
+        <v>-0.2418161877429554</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.07227787185153289</v>
+        <v>0.06763366410294225</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2489095300418711</v>
+        <v>0.2441713998329718</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.3882780746950445</v>
+        <v>0.3917382041119808</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3242</v>
+        <v>3243</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.3889836351101295</v>
+        <v>-0.3924639420822658</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4172430333586163</v>
+        <v>-0.4208271620006414</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.05782715068382771</v>
+        <v>-0.06155082857448946</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.2490863017512694</v>
+        <v>-0.2527442762311978</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1556648403529977</v>
+        <v>-0.1593905623869958</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1798375537506018</v>
+        <v>-0.183537434826512</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.4017116929278401</v>
+        <v>-0.405351170568558</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3903564128888775</v>
+        <v>-0.3940335653319309</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1881064784713402</v>
+        <v>-0.191852141397213</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.03544810918371866</v>
+        <v>-0.03930143575404799</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3153822652847751</v>
+        <v>-0.3191655815655636</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.04451353695301208</v>
+        <v>0.04061959064208764</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.07331490278138375</v>
+        <v>0.06938094030053321</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.278846718910998</v>
+        <v>0.2817709533527335</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3355</v>
+        <v>3356</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.5041271563144818</v>
+        <v>-0.5070365410716065</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5855584137207117</v>
+        <v>-0.5885391782300147</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.102970360507598</v>
+        <v>-0.1061191275988378</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2834462293029958</v>
+        <v>-0.2865354711225478</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.3598917662307386</v>
+        <v>-0.3629914096881919</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.3435832935891128</v>
+        <v>-0.3466720927438942</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.5608967183298859</v>
+        <v>-0.5639275332483962</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.6846899225908629</v>
+        <v>-0.6877129091248904</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5509047391368682</v>
+        <v>-0.5539727716928482</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.4023182185834884</v>
+        <v>-0.4054819393691034</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6202724569114224</v>
+        <v>-0.6233850142995081</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2714245602632843</v>
+        <v>-0.2746407035200917</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.2578375160894453</v>
+        <v>-0.2610841019194439</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.08072231310269729</v>
+        <v>-0.07814057517281725</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3429</v>
+        <v>3430</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.4887898600124174</v>
+        <v>-0.4913720282108045</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.5450003086464719</v>
+        <v>-0.5476512229590185</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1103457560498953</v>
+        <v>-0.1131449410762642</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.196902877910631</v>
+        <v>-0.1996716205788118</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3705269072267612</v>
+        <v>-0.3732746436529339</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.4354540350289895</v>
+        <v>-0.4381688911341257</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.6499388719900168</v>
+        <v>-0.652597203557967</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.839379795770121</v>
+        <v>-0.8420087818487971</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.7098371239719867</v>
+        <v>-0.7125084539146869</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.6410827032140816</v>
+        <v>-0.6438198487902937</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.8588218765210058</v>
+        <v>-0.861507775475971</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5459719222010548</v>
+        <v>-0.5487486682176979</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4835157322081756</v>
+        <v>-0.4863341417054485</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.3340624786669437</v>
+        <v>-0.3316875924813587</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3483</v>
+        <v>3484</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3195252767317172</v>
+        <v>-0.3219226076004134</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.399718657065506</v>
+        <v>-0.4021707734837605</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.006463352993485216</v>
+        <v>-0.009048043403296901</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1468963305243278</v>
+        <v>-0.1494360007121998</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.2688734645035353</v>
+        <v>-0.2714051380151474</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3854563978111543</v>
+        <v>-0.3879418950983222</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.5406127080958285</v>
+        <v>-0.5430591228855022</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.7056594695045391</v>
+        <v>-0.7080821462926963</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5503586491412378</v>
+        <v>-0.5528300635649828</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.4957883466046056</v>
+        <v>-0.4983172386264201</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.7419708560555236</v>
+        <v>-0.7444402705300064</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.4907910182394915</v>
+        <v>-0.4933321971385709</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.46450337082603</v>
+        <v>-0.4670735139662128</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3134901148119127</v>
+        <v>-0.3113195961767232</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3548</v>
+        <v>3549</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2890013642987128</v>
+        <v>-0.2911350086365445</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2286074387922099</v>
+        <v>-0.2308272008236756</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.07448024640189743</v>
+        <v>-0.07676114880265317</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1818815824865325</v>
+        <v>-0.1841279938741636</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1990242634218902</v>
+        <v>-0.2012898009409412</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3080196079169042</v>
+        <v>-0.310243112290685</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4899959167006926</v>
+        <v>-0.4921730101463027</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.604279668722171</v>
+        <v>-0.6064455635709223</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.5091978649996562</v>
+        <v>-0.5113942655839239</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.3867120348469015</v>
+        <v>-0.3889801233316845</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.5194611527615152</v>
+        <v>-0.5217017591479589</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.187681110586972</v>
+        <v>-0.1900148928407148</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.2258403881906048</v>
+        <v>-0.2281824920816788</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1011364084054307</v>
+        <v>-0.09925649662796587</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3592</v>
+        <v>3593</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3436463645927788</v>
+        <v>-0.3455860249880445</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.331427027513854</v>
+        <v>-0.3334336076481108</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.2672966819578946</v>
+        <v>-0.2693374373210276</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2885614327602184</v>
+        <v>-0.2905923003740725</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.2565630238183871</v>
+        <v>-0.2586247585046451</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3050512289642811</v>
+        <v>-0.3070890201332688</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.458052366198892</v>
+        <v>-0.4600520252694054</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.5488496370939018</v>
+        <v>-0.5508433080608128</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.4834626246763989</v>
+        <v>-0.4854779105026452</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.345061652540231</v>
+        <v>-0.3471495989266629</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3952312251695744</v>
+        <v>-0.3973143016125533</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.01140923335809418</v>
+        <v>-0.01359883890931002</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.02929708247278029</v>
+        <v>0.02707862386272808</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.09992419727472424</v>
+        <v>0.1015974069384811</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3631</v>
+        <v>3632</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2980486385414807</v>
+        <v>-0.2998460716866163</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3306501434404936</v>
+        <v>-0.3324972937408788</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2439772899630199</v>
+        <v>-0.2458633518887652</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2361476939252043</v>
+        <v>-0.2380322197895737</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.182773996960762</v>
+        <v>-0.1846934795194386</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3374548196943223</v>
+        <v>-0.3393221299837137</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5172206557228378</v>
+        <v>-0.5190425904429929</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6120702299659655</v>
+        <v>-0.6138838478479158</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5480562400012374</v>
+        <v>-0.5498906238253483</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4477892743973229</v>
+        <v>-0.4496827880253988</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.472128217950619</v>
+        <v>-0.4740234067928455</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.1471295158548074</v>
+        <v>-0.1491139056220092</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.08387727392996425</v>
+        <v>-0.08589524257306635</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.04372353961203146</v>
+        <v>0.04528226405786739</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2108296245577961</v>
+        <v>-0.2125107058943101</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3132206855526007</v>
+        <v>-0.3149282105547044</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.285633766470113</v>
+        <v>-0.2873627717400069</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.2766169006906551</v>
+        <v>-0.2783449389899815</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.2562532924204746</v>
+        <v>-0.2580056361091252</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3248924988055464</v>
+        <v>-0.3266172070502762</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4220688632510132</v>
+        <v>-0.4237708461310845</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.5477675705981113</v>
+        <v>-0.5494517644411445</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.4849616952526361</v>
+        <v>-0.4866659135784488</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4484787184468786</v>
+        <v>-0.4502220576386406</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3928437129951519</v>
+        <v>-0.394609943824058</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.1796964350220094</v>
+        <v>-0.1815205285099921</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.03941006376849998</v>
+        <v>-0.04128734085269059</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.00759102408071044</v>
+        <v>0.009041938153139029</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3700</v>
+        <v>3701</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.271515346873052</v>
+        <v>-0.2730538872925621</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1987619331742323</v>
+        <v>-0.2003703702989625</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2018477645350316</v>
+        <v>-0.2034683359394265</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.1108673993466027</v>
+        <v>-0.112509318685639</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.06846932077957035</v>
+        <v>-0.07014007419478219</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1877373131066733</v>
+        <v>-0.1893676089048881</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.2847659131759741</v>
+        <v>-0.2863734923675736</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4674348557813772</v>
+        <v>-0.4690083889854151</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.405710021573725</v>
+        <v>-0.4073029215194381</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.4041025354987369</v>
+        <v>-0.4057229264521993</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3507760471141097</v>
+        <v>-0.3524180045510263</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.1932357784102336</v>
+        <v>-0.1949200771490283</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.03093140979275688</v>
+        <v>-0.03267340297110621</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.04490704203485762</v>
+        <v>0.0462419403925054</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3739</v>
+        <v>3740</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1213700899327961</v>
+        <v>-0.1228025213417041</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.09274853674661188</v>
+        <v>-0.09423431976023267</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.07321397310415279</v>
+        <v>-0.07471675015540313</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.03513831004409695</v>
+        <v>-0.03664836476485789</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.02791712621701237</v>
+        <v>0.02637443209944479</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.06029987232341227</v>
+        <v>-0.06181148694478367</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.1037761665011345</v>
+        <v>-0.1052793182148761</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2893596816149966</v>
+        <v>-0.2908271411448951</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.202156265388389</v>
+        <v>-0.2036494803779121</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2360855200071867</v>
+        <v>-0.2375942714814343</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1854038995220435</v>
+        <v>-0.1869327127839284</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.0291033408409902</v>
+        <v>-0.03067374474458973</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.04695619682317442</v>
+        <v>0.0453528660171898</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.09788406291774265</v>
+        <v>0.09908211800023281</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3781</v>
+        <v>3782</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.04219952210771538</v>
+        <v>-0.04349837572539172</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.05808338057735085</v>
+        <v>-0.05941893962348388</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.01675827690162635</v>
+        <v>-0.01811526949216358</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.07511002910679565</v>
+        <v>0.07373138207058361</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.1842995627249309</v>
+        <v>0.1828779618545653</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.07400656992725629</v>
+        <v>0.07262080834446039</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.03010828384675079</v>
+        <v>0.02873129486782489</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1321568554191401</v>
+        <v>-0.1335033981421532</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.07296911163705744</v>
+        <v>-0.0743334977615433</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.06308094007974319</v>
+        <v>-0.06446994027469088</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.06804288806759473</v>
+        <v>-0.06943641586544658</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.06050108329000636</v>
+        <v>0.05907374193029824</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.2103957373430063</v>
+        <v>0.2089175068013844</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2106790028345884</v>
+        <v>0.2117181055234596</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3804</v>
+        <v>3805</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.03472515896215356</v>
+        <v>0.03348941734411426</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.01696161870882662</v>
+        <v>-0.01822211311874611</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.07416916363677473</v>
+        <v>0.07287491931973733</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.0876352091450201</v>
+        <v>0.08633983969124159</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1666955735945663</v>
+        <v>0.1653662247718586</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1637898576627492</v>
+        <v>0.1624675830569871</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.09342885008403101</v>
+        <v>0.09212239469094641</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.07066038351324266</v>
+        <v>-0.07193538668640542</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.01407138257987128</v>
+        <v>0.01277206505974959</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.007472501195600501</v>
+        <v>-0.008786768783139109</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.01264051976409064</v>
+        <v>0.01131550181047913</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1669109715960886</v>
+        <v>0.1655455744453391</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.2871060137682306</v>
+        <v>0.2856984816218073</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.3152057318919077</v>
+        <v>0.3161480388614706</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3834</v>
+        <v>3835</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1189869462314093</v>
+        <v>0.1178365682182445</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1071565535652326</v>
+        <v>0.1059742995887234</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2725510897480348</v>
+        <v>0.2713168192598872</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3129947613070243</v>
+        <v>0.3117521553911899</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.3612721208558369</v>
+        <v>0.3600048500895028</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.3607622940850632</v>
+        <v>0.3595009049049054</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.2643054237481124</v>
+        <v>0.2630667207540682</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.09789276609305375</v>
+        <v>0.09668678849251933</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.181529612566834</v>
+        <v>0.1802999521988582</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2577736441619649</v>
+        <v>0.2565053092943614</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2501356241487827</v>
+        <v>0.248864273273206</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.3513927486266937</v>
+        <v>0.3500951254658133</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.4413325084477435</v>
+        <v>0.4400017961293372</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.4712065810104491</v>
+        <v>0.4720192506582137</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3868</v>
+        <v>3869</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1476335684785113</v>
+        <v>0.1465955614285548</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1475653864133903</v>
+        <v>0.1464961758091903</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.2822797108349988</v>
+        <v>0.2811677287601881</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.297726799180154</v>
+        <v>0.2966127850160163</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.4440276254560231</v>
+        <v>0.4428650733720474</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.394553174200496</v>
+        <v>0.3934085131157801</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.3240143369175641</v>
+        <v>0.3228857112286931</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.1549773900820455</v>
+        <v>0.1538829151732415</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2631790275998824</v>
+        <v>0.2620549212231182</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2796568133401252</v>
+        <v>0.2785116425718073</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2444600133793386</v>
+        <v>0.2433194604187179</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.4743271144739936</v>
+        <v>0.4731272858463242</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.5856616341192122</v>
+        <v>0.5844244155137588</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.5916523395557505</v>
+        <v>0.5923350830881589</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3881</v>
+        <v>3882</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1516566977663985</v>
+        <v>0.1506629168340652</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1205210747887762</v>
+        <v>0.1195054778399225</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1763783530349343</v>
+        <v>0.1753407223172161</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2949831327749948</v>
+        <v>0.293916897311199</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.3618741569418873</v>
+        <v>0.3607804064776658</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.3135382399080413</v>
+        <v>0.3124618187154127</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2429311031461623</v>
+        <v>0.2418707769362385</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.0471493693003282</v>
+        <v>0.04613035975042834</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2576908298164042</v>
+        <v>0.256616037869037</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2712673731325026</v>
+        <v>0.2701730369806725</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.2612475494186626</v>
+        <v>0.2601515227053284</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.5162177914526112</v>
+        <v>0.5150562189651495</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.651542839686023</v>
+        <v>0.6503381812759983</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.6841334882698078</v>
+        <v>0.6847551957180542</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3899</v>
+        <v>3900</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1906107595446258</v>
+        <v>0.1896691981904084</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1266423751867976</v>
+        <v>0.1256892874447644</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1548508180296864</v>
+        <v>0.1538833313297303</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.2479217381679675</v>
+        <v>0.2469321978949921</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.2352470812445517</v>
+        <v>0.2342511330476</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2396619638804793</v>
+        <v>0.2386694792259192</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1689708141321091</v>
+        <v>0.1679945009086765</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.02313551043791051</v>
+        <v>0.02218808670421168</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1299598198014635</v>
+        <v>0.1289835309440477</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1651417020567933</v>
+        <v>0.1641414017706353</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1541963712486591</v>
+        <v>0.1531948899992699</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.3824868853404055</v>
+        <v>0.3814269992721719</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.5664954810683369</v>
+        <v>0.5653807329491016</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.5744191137372354</v>
+        <v>0.5750179468772387</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/ma/ma_ratio_200.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_200.xlsx
@@ -572,49 +572,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.129034207516753</v>
+        <v>-2.50182515648023</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.860419269215079</v>
+        <v>-8.234087194068799</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-8.943506302136058</v>
+        <v>-9.32101951050042</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.815952577200783</v>
+        <v>-9.193895266439725</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-10.73164350573155</v>
+        <v>-11.07032819617202</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-7.684894296142666</v>
+        <v>-8.029054427900157</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-10.5252202601132</v>
+        <v>-10.86459128642986</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.92883920330582</v>
+        <v>-9.25270080384459</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-8.99186323980247</v>
+        <v>-8.598268442104192</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-9.154420420686435</v>
+        <v>-8.729871719665304</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-10.73951280435539</v>
+        <v>-10.32386109579558</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-12.08637737419736</v>
+        <v>-12.35049998816792</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-12.50952995149133</v>
+        <v>-12.74872301613924</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-10.21808550139893</v>
+        <v>-10.41964996022213</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>160</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.717519138278043</v>
+        <v>-3.746638876514957</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-7.815363344939442</v>
+        <v>-7.816628933061672</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.602932087330679</v>
+        <v>-2.603114979023353</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.343644439642368</v>
+        <v>-4.344179638116429</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.882066990410529</v>
+        <v>-4.83369655141842</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-5.210584692632295</v>
+        <v>-5.186723848899661</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-5.296709590577152</v>
+        <v>-5.248834278472614</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.140903331851241</v>
+        <v>-5.091772065672203</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.33065232321465</v>
+        <v>-3.257522406199925</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.307803465973393</v>
+        <v>-2.208585667017772</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.888445422174115</v>
+        <v>-1.788634126739197</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.01948772328648118</v>
+        <v>0.1431077039650503</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.275031556097488</v>
+        <v>-2.126390118333262</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.4500179468775301</v>
+        <v>0.6220167064434818</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>194</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.637119047984683</v>
+        <v>1.798756852552856</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.142650151611164</v>
+        <v>4.284527834489538</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.694665704317188</v>
+        <v>1.826656238440513</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.450712594395149</v>
+        <v>7.105014026561484</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.457752104146685</v>
+        <v>7.636839032545545</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.242040609760998</v>
+        <v>8.201160715902766</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.673827877929376</v>
+        <v>8.657497926855854</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6.180208743625329</v>
+        <v>6.926417302956224</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10.23880235959714</v>
+        <v>10.77831020766347</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.907465310099553</v>
+        <v>10.23663079805638</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>10.73588410399157</v>
+        <v>10.83572073796383</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>12.83412254804285</v>
+        <v>12.95775884409291</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>12.93319703570764</v>
+        <v>13.0818476654068</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>11.61625506027931</v>
+        <v>11.27278990232032</v>
       </c>
     </row>
     <row r="9">
@@ -728,413 +728,413 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.741458218384139</v>
+        <v>-3.321085337098872</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.323100969658476</v>
+        <v>-3.288207444874217</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.526285401578967</v>
+        <v>-3.491217515505468</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.8869465427586931</v>
+        <v>-1.315258851565183</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.756178777609854</v>
+        <v>-3.448127774372487</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.528712688325946</v>
+        <v>-5.375628107599312</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.168493168772862</v>
+        <v>-6.338573136066564</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.998879756831109</v>
+        <v>-3.131487973790335</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.61137528245672</v>
+        <v>-3.902139852585279</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.61714826174763</v>
+        <v>-5.836014941022299</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.703575800464399</v>
+        <v>-3.836210853204022</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.273524007281608</v>
+        <v>-7.617733801150045</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-6.483662850119579</v>
+        <v>-8.178684021551085</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-7.570020221061689</v>
+        <v>-9.194159764144331</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.1168</t>
+          <t>X ≈ -0.1169</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.8860013399247251</v>
+        <v>-0.9101118248869824</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-4.111159243798717</v>
+        <v>-4.093288910042752</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.704508379046182</v>
+        <v>-3.687026898357452</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.973715358855799</v>
+        <v>-3.957142857142863</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.112700688689088</v>
+        <v>-4.046391998094784</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-3.011218506699258</v>
+        <v>-2.973606479275759</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.292971814831013</v>
+        <v>-2.234262568501308</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.768200487267372</v>
+        <v>-4.700095328884657</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.230405369086178</v>
+        <v>-5.137067938021367</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-7.064259908388038</v>
+        <v>-7.160896518836438</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-8.875386769459475</v>
+        <v>-8.96503696637253</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-10.04582789421249</v>
+        <v>-10.10687022900754</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-11.67079802463443</v>
+        <v>-11.70202815557145</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-10.64184952300227</v>
+        <v>-10.65298329355609</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.05832</t>
+          <t>X ≈ -0.05835</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>281</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.08233951807884</v>
+        <v>-4.111535312431471</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.846550522174695</v>
+        <v>-2.847737308619351</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.885450020808733</v>
+        <v>-2.885603410813054</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.958071852309345</v>
+        <v>-5.958566344687348</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.225898771953162</v>
+        <v>-2.17735285218739</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.996140400680979</v>
+        <v>-2.972182991731366</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.50433830443113</v>
+        <v>-4.456326625440809</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-7.106638264943854</v>
+        <v>-7.057390702550137</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.676517218619651</v>
+        <v>-4.603260108839955</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.102948470465527</v>
+        <v>-4.003601145170954</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.375265287088709</v>
+        <v>-5.275357251070034</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.629143362491469</v>
+        <v>-4.505446741463224</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.337550443562733</v>
+        <v>-4.188860895784906</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.467686679457273</v>
+        <v>-4.295687919890611</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.000215</t>
+          <t>X ≈ 0.000165</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>191</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.360497182366814</v>
+        <v>-5.389692976719445</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.306761809462053</v>
+        <v>-3.307948595906709</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.5601719376725995</v>
+        <v>-0.5603253276769209</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.09361341533985268</v>
+        <v>0.09311892296184965</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.015356766027978</v>
+        <v>-1.966810846262206</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-5.382904202361587</v>
+        <v>-5.358946793411974</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-7.038295189900012</v>
+        <v>-6.990283510909691</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-8.028924043110834</v>
+        <v>-7.979676480717117</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-10.70770724675403</v>
+        <v>-10.63445013697433</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-9.986945414811636</v>
+        <v>-9.887598089517063</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-9.668086363647866</v>
+        <v>-9.568178327629191</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-11.20438883956468</v>
+        <v>-11.08069221853643</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-10.05385906460595</v>
+        <v>-9.905169516828124</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-11.39880404265156</v>
+        <v>-11.22680528308489</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 0.05875</t>
+          <t>X ≈ 0.05868</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>209</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.241681580773481</v>
+        <v>-2.270877375126112</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.4533524218563585</v>
+        <v>0.4521656354117027</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.407863333752154</v>
+        <v>3.407709943747832</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.6672750802113256</v>
+        <v>0.6667805878333226</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.999798924244821</v>
+        <v>3.048344844010593</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.297172953879802</v>
+        <v>3.321130362829415</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.212462594613633</v>
+        <v>3.260474273603954</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.788456151783713</v>
+        <v>1.83770371417743</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.72747399526105</v>
+        <v>1.800731105040747</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3990862994095536</v>
+        <v>0.498433624704127</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.7625526578935933</v>
+        <v>-0.662644621874918</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.14263889159092</v>
+        <v>2.266335512619165</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.7655502392344431</v>
+        <v>0.9142397870122707</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.469754788982513</v>
+        <v>1.641753548549175</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 0.1173</t>
+          <t>X ≈ 0.1172</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.68706297209026</v>
+        <v>3.542519754060329</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.288475304223404</v>
+        <v>1.169868984693942</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.993441452276613</v>
+        <v>2.881394154273984</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.386133787466029</v>
+        <v>3.274436090225493</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.685114575577707</v>
+        <v>4.627292212431477</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.982488605212851</v>
+        <v>4.900077731250462</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8.309851736760301</v>
+        <v>8.260474273603947</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>9.417586242579979</v>
+        <v>9.373588881641716</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>9.881538469259212</v>
+        <v>9.862932061978576</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>11.65629158893992</v>
+        <v>11.67068242853205</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>12.50145919708393</v>
+        <v>12.51917355994333</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>14.11064049904549</v>
+        <v>14.1562876657292</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>15.79022717854048</v>
+        <v>15.86639289706012</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>17.06583159517121</v>
+        <v>17.16806933802288</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 0.1758</t>
+          <t>X ≈ 0.1757</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5.876855230462688</v>
+        <v>5.96942033885567</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.145434533293248</v>
+        <v>5.26343623615606</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9383464329957789</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.3977040832399013</v>
+        <v>-0.2635756056808702</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.229248768300472</v>
+        <v>-1.04522240745154</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.744191454207872</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.655881285614768</v>
+        <v>-3.464671925226462</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.002715325295966</v>
+        <v>-4.807697668065913</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.770442349853937</v>
+        <v>-4.552272616384052</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.860830354394942</v>
+        <v>-3.621715232286725</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-5.238552040514371</v>
+        <v>-4.995446323097674</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.617663624229429</v>
+        <v>-4.352484264095345</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.105263157894747</v>
+        <v>-1.823665582472046</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.9997621117737836</v>
+        <v>-0.6974277380005702</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.2344</t>
+          <t>X ≈ 0.2343</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>214</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-6.219233787543644</v>
+        <v>-6.248429581896275</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-6.89584044135519</v>
+        <v>-6.897027227799846</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.421452947605559</v>
+        <v>-5.42160633760988</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.889358645138692</v>
+        <v>-3.889853137516695</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5.829517357112834</v>
+        <v>-5.780971437347063</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.8592461312161177</v>
+        <v>-0.8352887222665046</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.214984527865468</v>
+        <v>-4.166972848875147</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.812894293147579</v>
+        <v>-2.763646730753862</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.808455888922651</v>
+        <v>-3.735198779142955</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-4.658374685252511</v>
+        <v>-4.559027359957938</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.361407971531207</v>
+        <v>-4.237711350502963</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-5.248848544470789</v>
+        <v>-5.100158996692961</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-5.490402613870415</v>
+        <v>-5.318403854303753</v>
       </c>
     </row>
     <row r="17">
@@ -1147,670 +1147,670 @@
         <v>209</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6291318163556525</v>
+        <v>0.5999360220030212</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.759572517550197</v>
+        <v>4.758385731105541</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.407863333752047</v>
+        <v>3.407709943747726</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.14574397973275</v>
+        <v>1.145249487354747</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.085923326158536</v>
+        <v>1.134469245924308</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.297172953879745</v>
+        <v>3.321130362829358</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.255524795570565</v>
+        <v>2.303536474560886</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.180800649391479</v>
+        <v>4.230048211785196</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.076756291911771</v>
+        <v>5.150013401691467</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>6.14071309366809</v>
+        <v>6.240060418962663</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.892949734450902</v>
+        <v>6.992857770469577</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>6.927327886806225</v>
+        <v>7.05102450783447</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.464114832535884</v>
+        <v>7.612804380313712</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.819037085633227</v>
+        <v>4.991035845199889</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.3514</t>
+          <t>X ≈ 0.3513</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>194</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.189187062249097</v>
+        <v>3.159991267896466</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.670784474339875</v>
+        <v>4.669597687895219</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>6.853332677213793</v>
+        <v>6.853179287209471</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.890774315647519</v>
+        <v>3.890279823269516</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.898876515129167</v>
+        <v>4.947422434894939</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.680786627238504</v>
+        <v>4.704744036188117</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7.17339585560115</v>
+        <v>7.221407534591471</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>8.252718964391725</v>
+        <v>8.301966526785442</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>7.160808972817406</v>
+        <v>7.234066082597103</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>6.826354094013261</v>
+        <v>6.925701419307835</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>5.075261183175783</v>
+        <v>5.175169219194458</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>5.625103253056906</v>
+        <v>5.748799874085151</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.689488482217698</v>
+        <v>4.838178029995525</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.884296297392709</v>
+        <v>4.056295056959371</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.4099</t>
+          <t>X ≈ 0.4098</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>133</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.608735579406492</v>
+        <v>-3.637931373759123</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7951159215146504</v>
+        <v>0.7939291350699946</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.904103935255804</v>
+        <v>1.903950545251483</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.034329078844166</v>
+        <v>2.033834586466163</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.496039525748515</v>
+        <v>1.544585445514286</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4.049052653127916</v>
+        <v>4.073010062077529</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.050695300123216</v>
+        <v>-2.002683621132896</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4897548530825233</v>
+        <v>0.5390024154762401</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.578746100432731</v>
+        <v>-2.505488990653035</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.676785197514462</v>
+        <v>-2.577437872219889</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.129606656526498</v>
+        <v>-2.029698620507823</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.5914691056749817</v>
+        <v>-0.467772484646737</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.019138755980826</v>
+        <v>-3.870449208202999</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.289643707258094</v>
+        <v>-2.117644947691431</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.4684</t>
+          <t>X ≈ 0.4682</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>113</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.80834965885299</v>
+        <v>-3.837545453205621</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-5.419535751916719</v>
+        <v>-5.420722538361375</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.389528375609849</v>
+        <v>-1.389681765614171</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.259303232021487</v>
+        <v>-1.25979772439949</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-6.22237154617914</v>
+        <v>-6.173825626413368</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-5.040041764331662</v>
+        <v>-5.016084355382048</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-5.12475212359783</v>
+        <v>-5.076740444607509</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-9.131643776234128</v>
+        <v>-9.082396213840411</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-10.96253743718168</v>
+        <v>-10.88928032740198</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-10.92750048129916</v>
+        <v>-10.82815315600458</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-9.362290135134565</v>
+        <v>-9.262382099115889</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-9.327911982779241</v>
+        <v>-9.204215361750997</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-9.74806283609265</v>
+        <v>-9.599373288314823</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-10.40728293807851</v>
+        <v>-10.23528417851185</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.527</t>
+          <t>X ≈ 0.5268</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2217866721684203</v>
+        <v>0.9145457093595155</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.313303281807222</v>
+        <v>0.701231637902211</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.4328194542991639</v>
+        <v>0.3074936495875846</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.751459743343176</v>
+        <v>3.177103718199604</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.8408838638064182</v>
+        <v>-1.421734463848281</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.597563888225388</v>
+        <v>-5.258537986125248</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.682274247491556</v>
+        <v>-3.949331061652074</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-7.852045593981074</v>
+        <v>-7.154889849432521</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-7.913027750503929</v>
+        <v>-7.191862458569318</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-11.46564924953641</v>
+        <v>-10.75541706678165</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-11.6703504077966</v>
+        <v>-10.95955751431774</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-12.98732360679271</v>
+        <v>-12.27125379065147</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-10.70477175740334</v>
+        <v>-9.926685689818036</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-11.83038745852816</v>
+        <v>-11.04750384150122</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.5856</t>
+          <t>X ≈ 0.5854</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>10.48204693242861</v>
+        <v>9.308069993295042</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>8.870860839364674</v>
+        <v>9.543074726320896</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>6.624237602757994</v>
+        <v>5.512973101642665</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.05075904264266</v>
+        <v>3.824675324675319</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>6.216173193250455</v>
+        <v>6.971789820087139</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.809843519181733</v>
+        <v>3.608211702542327</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>6.428836863619274</v>
+        <v>5.365737431498687</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>7.813620071684589</v>
+        <v>6.718086489297058</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>9.604489767013774</v>
+        <v>8.499295698342081</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>8.754570970683801</v>
+        <v>7.675467117527198</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>6.698017960571761</v>
+        <v>5.653144851809287</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.028692409223588</v>
+        <v>2.074947952810653</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.7566897040581182</v>
+        <v>-0.1383917919350992</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.9824253542846506</v>
+        <v>0.1106530700801684</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.6441</t>
+          <t>X ≈ 0.6439</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>65</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.365237815619402</v>
+        <v>1.336042021266771</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>8.984820953324892</v>
+        <v>8.983634166880236</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.717642739122546</v>
+        <v>-3.717796129126867</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.048956057072502</v>
+        <v>-2.049450549450505</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.566600543677957</v>
+        <v>3.615146463443729</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.863974573313087</v>
+        <v>3.8879319822627</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.240802675585421</v>
+        <v>2.288814354575742</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.712751875275771</v>
+        <v>1.786008985055467</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.478217694330532</v>
+        <v>5.577565019625105</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>11.42736268991649</v>
+        <v>11.52727072593517</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>16.07712545765639</v>
+        <v>16.20082207868463</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>12.58005152741994</v>
+        <v>12.72874107519777</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>11.26732563918498</v>
+        <v>11.43932439875164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.7026</t>
+          <t>X ≈ 0.7024</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>44</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-4.753643303261626</v>
+        <v>-4.782839097614257</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-8.637556669052728</v>
+        <v>-8.638743455497384</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-15.85050987198959</v>
+        <v>-15.85066326199391</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-8.902102910219405</v>
+        <v>-8.902597402597408</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-4.894937917860616</v>
+        <v>-4.846391998094845</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>-0.02815193382131298</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.135907570690122</v>
+        <v>2.183919249680443</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.941566199630721</v>
+        <v>3.990813762024437</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.607856770380671</v>
+        <v>1.681113880160368</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.030665246778085</v>
+        <v>3.130012572072658</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>9.644145906699706</v>
+        <v>9.744053942718381</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>14.22397860450952</v>
+        <v>14.34767522553776</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>20.62200956937798</v>
+        <v>20.77069911715581</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>16.30229067414991</v>
+        <v>16.47428943371657</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.7611</t>
+          <t>X ≈ 0.7609</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>39</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.929340379722056</v>
+        <v>3.900144585369425</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2459482774443345</v>
+        <v>-0.2471350638889902</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.923382901903267</v>
+        <v>1.923229511898946</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.617710609593971</v>
+        <v>4.617216117215968</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>6.643523620600988</v>
+        <v>6.692069540366759</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-3.315512606174188</v>
+        <v>-3.291555197224575</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.964325529542919</v>
+        <v>-5.916313850552598</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-6.431394173329657</v>
+        <v>-6.382146610935941</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-6.492376329852505</v>
+        <v>-6.419119220072808</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-9.906397690284855</v>
+        <v>-9.807050364990282</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-7.546996284442557</v>
+        <v>-7.447088248423881</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-12.64082326029229</v>
+        <v>-12.51712663926404</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-10.49687154950313</v>
+        <v>-10.34818200172531</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-5.142930771071477</v>
+        <v>-4.970932011504814</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.8196</t>
+          <t>X ≈ 0.8194</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>8.630195080576762</v>
+        <v>7.489888175113016</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.463453431957376</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-4.486873508353298</v>
+        <v>-3.058455469786196</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-4.356648364764702</v>
+        <v>-2.928571428571345</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-7.672715695638331</v>
+        <v>-6.274963426666211</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.206614641397252</v>
+        <v>11.08002314578439</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.961768219832742</v>
+        <v>7.757047528258198</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.900786063310044</v>
+        <v>7.72007491912148</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.5046882885754513</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7.62394388649777</v>
+        <v>9.549248747913268</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.452789072258099</v>
+        <v>-1.821155943293263</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.460393407761828</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.647204275344976</v>
+        <v>-4.824411864984668</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.8781</t>
+          <t>X ≈ 0.8779</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-7.026370575988899</v>
+        <v>-5.451288295475223</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>10.61259344289834</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>9.149490128010413</v>
+        <v>7.277678983995401</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>18.37062436250788</v>
+        <v>16.23109243697486</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>20.8626378397153</v>
+        <v>18.68301976661119</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>15.09940580874431</v>
+        <v>13.07345234425364</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>15.01469544947807</v>
+        <v>13.01279625502811</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.487020745085175</v>
+        <v>6.664610553468201</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.426038588562484</v>
+        <v>6.627637944331489</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.545816761929686</v>
+        <v>2.862632892928353</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.341115603669408</v>
+        <v>2.658492445392184</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.685112304581246</v>
+        <v>-3.165693758419394</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.9250398724082061</v>
+        <v>2.321501256193159</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.181078552937855</v>
+        <v>5.51172258879685</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.9367</t>
+          <t>X ≈ 0.9364</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>39</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>14.1857506361323</v>
+        <v>14.15655484177967</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>10.01046197896592</v>
+        <v>10.00927519252127</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>12.17979315831338</v>
+        <v>12.17963976830906</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.181813173696604</v>
+        <v>7.181318681318601</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>9.207626184703479</v>
+        <v>9.25617210446925</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>12.06910277844119</v>
+        <v>12.0930601873908</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>17.11259754738008</v>
+        <v>17.1606092263704</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>16.64552890359349</v>
+        <v>16.69477646598721</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>19.14864931117322</v>
+        <v>19.22190642095291</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>15.73462795074079</v>
+        <v>15.83397527603536</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>15.52992679248067</v>
+        <v>15.62983482849934</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>15.56430494483583</v>
+        <v>15.68800156586408</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>7.451846399214972</v>
+        <v>7.6005359469928</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.113479485338708</v>
+        <v>5.28547824490537</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.995</t>
+          <t>X ≈ 0.9949</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7.042893493275173</v>
+        <v>7.489888175112981</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.050755019258993</v>
+        <v>3.406711089957206</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.036936015456369</v>
+        <v>5.512973101642565</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9.929065920949462</v>
+        <v>13.14285714285718</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>14.1526811297585</v>
+        <v>15.15360800190522</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>12.06910277844113</v>
+        <v>15.42639352072405</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>11.98439241917509</v>
+        <v>15.36573743149876</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>13.89827615634068</v>
+        <v>17.39990467111534</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>11.45634161886555</v>
+        <v>14.86293206197855</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>15.36832758444039</v>
+        <v>19.03910348116349</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.4017216642754</v>
+        <v>13.83496303362737</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.055147435678442</v>
+        <v>11.39312977099237</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>14.77785372522207</v>
+        <v>18.49797184442847</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.24168461354397</v>
+        <v>13.74701670644398</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>12.73647527381348</v>
+        <v>11.48988817511307</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.777463093793003</v>
+        <v>5.906711089957049</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>15.07834388295107</v>
+        <v>13.51297310164234</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.165090765669866</v>
+        <v>-2.357142857142918</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.721024874382294</v>
+        <v>-2.846391998094781</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>14.96765350307888</v>
+        <v>9.426393520724204</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10.53511705685619</v>
+        <v>5.365737431498687</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>10.06804841306946</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>14.35489234350314</v>
+        <v>8.862932061978547</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.157147460216748</v>
+        <v>4.039103481163565</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>13.30027238891314</v>
+        <v>7.834963033627531</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>17.68247662822493</v>
+        <v>11.89312977099237</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>12.91449968795506</v>
+        <v>7.497971844428541</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>17.48806142513805</v>
+        <v>11.74701670644385</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>10.85241730279898</v>
+        <v>10.82322150844634</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>15.90789787640192</v>
+        <v>15.90671108995726</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>25.51312649164682</v>
+        <v>25.5129731016425</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>28.97668496856853</v>
+        <v>28.97619047619052</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>25.10506208213945</v>
+        <v>25.15360800190522</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>25.40243611177453</v>
+        <v>25.42639352072415</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>21.98439241917504</v>
+        <v>22.03240409816536</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>21.5173237753883</v>
+        <v>21.56657133778202</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>21.45634161886552</v>
+        <v>21.52959872864522</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>33.93975615586895</v>
+        <v>34.03910348116352</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>30.40172166427547</v>
+        <v>30.50162970029415</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>23.76943314996412</v>
+        <v>23.89312977099237</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>20.01594896331738</v>
+        <v>20.16463851109521</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>20.24168461354392</v>
+        <v>20.41368337311058</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>34</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.401436910642119</v>
+        <v>3.372241116289487</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.731427288166479</v>
+        <v>4.730240501721823</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.395479432823251</v>
+        <v>1.39532604281893</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.415471894176669</v>
+        <v>-1.415966386554672</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.810944435080621</v>
+        <v>9.859490354846393</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.225965523539244</v>
+        <v>4.249922932488857</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.082431634861308</v>
+        <v>7.130443313851629</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.615362991074569</v>
+        <v>6.664610553468286</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.495557305140025</v>
+        <v>9.568814414919721</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.763285567633744</v>
+        <v>2.862632892928318</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.38259206121473</v>
+        <v>-0.2826840251960547</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>14.35766844408177</v>
+        <v>14.48136506511002</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>16.8786940613566</v>
+        <v>17.02738360913443</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>14.16325324099493</v>
+        <v>14.33525200056159</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>13</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.365237815619494</v>
+        <v>1.336042021266863</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-7.938255969752078</v>
+        <v>-7.939442756196733</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-31.40995043143014</v>
+        <v>-31.41010382143446</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5104945186110115</v>
+        <v>-0.5109890109890145</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-24.12570714862978</v>
+        <v>-24.07716122886401</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-23.8283331189947</v>
+        <v>-23.80437571004508</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-23.91304347826086</v>
+        <v>-23.86503179927054</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-32.0724198143553</v>
+        <v>-32.02317225196158</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.364171201647302</v>
+        <v>-1.290914091867606</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.214089997977112</v>
+        <v>-2.114742672682539</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.273516536070339</v>
+        <v>5.373424572089014</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>13.00020238073335</v>
+        <v>13.12389900176159</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>20.27235921972769</v>
+        <v>20.42104876750552</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>28.19040256226186</v>
+        <v>28.36240132182852</v>
       </c>
     </row>
     <row r="34">
@@ -2028,49 +2028,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>8.630195080576762</v>
+        <v>6.313417586877726</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.463453431957454</v>
+        <v>-1.152112439454555</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-7.42820336894578</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-9.912203920320458</v>
+        <v>-7.2983193277311</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-27.11716014008277</v>
+        <v>-25.43462729221239</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-15.70867499933657</v>
+        <v>-13.39713589104051</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-15.79338535860274</v>
+        <v>-13.45779198026597</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-2.158918858296374</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-27.43254727002337</v>
+        <v>-25.72530323213906</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-22.72691051079772</v>
+        <v>-20.66677887177765</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-22.93161166905787</v>
+        <v>-20.87091931931366</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-28.4527890722581</v>
+        <v>-26.69510552312528</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-17.76182881446044</v>
+        <v>-15.3255575673362</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-23.09164871978943</v>
+        <v>-20.95886564649725</v>
       </c>
     </row>
   </sheetData>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3900</v>
+        <v>3910</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.09144503641219615</v>
+        <v>-0.1012410627151752</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1043720622484869</v>
+        <v>-0.1157264419143331</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.02509902612361259</v>
+        <v>-0.03663159103797398</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.008822277808341994</v>
+        <v>-0.02040816326530859</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1494787211350399</v>
+        <v>-0.1640750805137614</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1195700294741826</v>
+        <v>-0.132565131649514</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2671219567314651</v>
+        <v>-0.2814415319937851</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.4130397678784732</v>
+        <v>-0.4269594759735185</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.3063557776346926</v>
+        <v>-0.296710339043166</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.4506126965900279</v>
+        <v>-0.4422455224133444</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.4873380333929944</v>
+        <v>-0.4788626755470773</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3361537285597151</v>
+        <v>-0.3553364866763502</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.2805562062972484</v>
+        <v>-0.3015679152237212</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.322417950558652</v>
+        <v>-0.345054904809281</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3755</v>
+        <v>3766</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.01276316429231628</v>
+        <v>-0.009450274212206011</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1951290948780553</v>
+        <v>0.1946941497771704</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.3192868740153401</v>
+        <v>0.3183742136361047</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3312666418752528</v>
+        <v>0.3303571428571388</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.2591534742754789</v>
+        <v>0.2529457502495873</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1725663270283206</v>
+        <v>0.1693717931141876</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1289963532526528</v>
+        <v>0.1232248420473212</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.08420064187662035</v>
+        <v>-0.08949087501402886</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.02903665432651792</v>
+        <v>0.02071514338931735</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1145135967247839</v>
+        <v>-0.1253527522581948</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.09144846167806264</v>
+        <v>-0.1024208878371056</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1175832697405426</v>
+        <v>0.1033208537949193</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1916678131576361</v>
+        <v>0.1743721629844188</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.05970503076540012</v>
+        <v>0.04016593639610733</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3595</v>
+        <v>3606</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1521216634789582</v>
+        <v>0.1563706288295137</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.5516461436599229</v>
+        <v>0.5501605095259876</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4493439070655185</v>
+        <v>0.4480021312249889</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.5393294438343119</v>
+        <v>0.5377686472819221</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.4879699622726292</v>
+        <v>0.478642580051833</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.4121502388908311</v>
+        <v>0.4070244006355992</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.3704742255788744</v>
+        <v>0.3615857569899674</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.140854276175105</v>
+        <v>0.1324628106502246</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1785638410877368</v>
+        <v>0.16617216167392</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.01689847041608061</v>
+        <v>-0.03291867950125749</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.01147085008436477</v>
+        <v>-0.02760277407549694</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1219491355076272</v>
+        <v>0.1015554916132118</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3014513734026565</v>
+        <v>0.2764581211127677</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.04233366314984721</v>
+        <v>0.01434893051490604</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3401</v>
+        <v>3412</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.06741437368356884</v>
+        <v>0.06298759031769663</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.346807926211369</v>
+        <v>0.3378313005450551</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.3783082032528711</v>
+        <v>0.3696144123504794</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.2021320515353437</v>
+        <v>0.1643672394330835</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.09039932554120611</v>
+        <v>0.07164078879046798</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.02255931505995079</v>
+        <v>-0.03613575328053287</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.0461240127498499</v>
+        <v>-0.1101044425862341</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2036428619270296</v>
+        <v>-0.2538288574351668</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.3952927518528213</v>
+        <v>-0.4372143509057835</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5830044902396665</v>
+        <v>-0.6168262406519602</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.624521970663821</v>
+        <v>-0.645271226987461</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.6031792508586875</v>
+        <v>-0.6294244176426673</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4190892494986045</v>
+        <v>-0.45163260913138</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.617866498874001</v>
+        <v>-0.6257851692887968</v>
       </c>
     </row>
     <row r="10">
@@ -2422,257 +2422,257 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3139</v>
+        <v>3140</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.3853260076822096</v>
+        <v>0.3561302133295783</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.65312080633813</v>
+        <v>0.6519340198934742</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.7042092941945555</v>
+        <v>0.7040559041902341</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2930331638975616</v>
+        <v>0.2925386715195586</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.3279920184451797</v>
+        <v>0.3765379382109515</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.4024361117745414</v>
+        <v>0.4263935207241545</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.3814200200242936</v>
+        <v>0.4294316990146143</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.05380149000448853</v>
+        <v>-0.00455392761077178</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.2103250478011418</v>
+        <v>-0.1370679380214455</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2462903557589158</v>
+        <v>-0.1647181748873905</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.4509915140191083</v>
+        <v>-0.3688586224234811</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1298978471687207</v>
+        <v>-0.02406768123692871</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.08709688728467313</v>
+        <v>0.2177170673584783</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.03759753576053981</v>
+        <v>0.1164434580362652</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.08758</t>
+          <t>X &gt; -0.08761</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2890</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.4948625161784506</v>
+        <v>0.4656667218258193</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.063607218962375</v>
+        <v>1.062420432517719</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.084060747702139</v>
+        <v>1.083907357697818</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.6606526732974274</v>
+        <v>0.6601581809194244</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.710598414319378</v>
+        <v>0.7591443340851498</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.6965537588333603</v>
+        <v>0.7205111677829734</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.6118433995671921</v>
+        <v>0.6598550785575128</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3523872125278515</v>
+        <v>0.4016347749215683</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2222009037559474</v>
+        <v>0.2954580135356437</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3411402389139724</v>
+        <v>0.4404875642085457</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2748473851520501</v>
+        <v>0.3747554211707254</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.724450451002177</v>
+        <v>0.8481470720304216</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.100147348553826</v>
+        <v>1.248836896331653</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.8760560091609833</v>
+        <v>1.048054768727646</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.02905</t>
+          <t>X &gt; -0.02909</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2609</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.9878459472349093</v>
+        <v>0.958650152882278</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.484747243975605</v>
+        <v>1.483560457530949</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.511593337181466</v>
+        <v>1.511439947177145</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.373516449340165</v>
+        <v>1.373021956962162</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.026871204408522</v>
+        <v>1.075417124174294</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.094272064246745</v>
+        <v>1.118229473196358</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.162877151511815</v>
+        <v>1.210888830502135</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.155754847318789</v>
+        <v>1.205002409712506</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7498129361007315</v>
+        <v>0.8230700458804279</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.8197868189582991</v>
+        <v>0.9191341442528724</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.8833876921277763</v>
+        <v>0.9832957281464516</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.301054460811194</v>
+        <v>1.424751081839439</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.685809701786773</v>
+        <v>1.834499249564601</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.451599012419599</v>
+        <v>1.623597771986262</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.02948</t>
+          <t>X &gt; 0.02942</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2418</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.489307294527684</v>
+        <v>1.460111500175053</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.863232863994874</v>
+        <v>1.862046077550218</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.675243944086809</v>
+        <v>1.675090554082487</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.474617143920007</v>
+        <v>1.474122651542004</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.267179534579476</v>
+        <v>1.315725454345248</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.605910057183969</v>
+        <v>1.629867466133582</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.810695148703566</v>
+        <v>1.858706827693887</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.881260913518979</v>
+        <v>1.930508475912696</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.654852785118621</v>
+        <v>1.728109894898317</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.673420341146084</v>
+        <v>1.772767666440657</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.716858140702271</v>
+        <v>1.816766176720947</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.288870701659739</v>
+        <v>2.412567322687984</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.613136721795456</v>
+        <v>2.761826269573284</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.466663935297426</v>
+        <v>2.638662694864088</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 0.08801</t>
+          <t>X &gt; 0.08794</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2209</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.8423071473742</v>
+        <v>1.813111353021569</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.996625807592402</v>
+        <v>1.995439021147746</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.511315717540846</v>
+        <v>1.511162327536525</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.551002155832691</v>
+        <v>1.550507663454688</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.103251308033514</v>
+        <v>1.151797227799285</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.445894690316862</v>
+        <v>1.469852099266475</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.678069799588492</v>
+        <v>1.726081478578813</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.890041445525618</v>
+        <v>1.939289007919335</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.647981878409809</v>
+        <v>1.721238988189505</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.793988840341612</v>
+        <v>1.893336165636185</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.951442503267472</v>
+        <v>2.051350539286148</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.302706124160594</v>
+        <v>2.426402745188838</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.787942323812331</v>
+        <v>2.936631871590158</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.560984447556287</v>
+        <v>2.732983207122949</v>
       </c>
     </row>
     <row r="15">
@@ -2682,777 +2682,777 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.45781482285733</v>
+        <v>1.453802882603448</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.144221727605313</v>
+        <v>2.166962593511023</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.202404390990331</v>
+        <v>1.226477748990739</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.168515749020706</v>
+        <v>1.192337733343741</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.3567032199950262</v>
+        <v>0.4297151642890356</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.7087818448161087</v>
+        <v>0.7571753687285181</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2958439144339735</v>
+        <v>0.3684711657797166</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3211166273211816</v>
+        <v>0.3947105759813923</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.06809310031756155</v>
+        <v>0.02968985312124062</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.2615567544154729</v>
+        <v>-0.1380425002470389</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.2474395319316827</v>
+        <v>-0.1234842053009046</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1583567843903637</v>
+        <v>-0.01064278231545046</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.07794750452817567</v>
+        <v>0.2502955185674125</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.4621811778492315</v>
+        <v>-0.2661052181050323</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.2051</t>
+          <t>X &gt; 0.205</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1487</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.4444370293177045</v>
+        <v>0.4152412349650731</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.455981265776401</v>
+        <v>1.454794479331746</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.262958367907707</v>
+        <v>1.262804977903386</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.527682502753635</v>
+        <v>1.527188010375632</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.7203949671428163</v>
+        <v>0.7689408869085881</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.959261935580855</v>
+        <v>1.983219344530468</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.202056620026859</v>
+        <v>1.25006829901718</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.541981923785507</v>
+        <v>1.591229486179223</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.010253297861262</v>
+        <v>1.083510407640958</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5638314753040987</v>
+        <v>0.6631788005986721</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.8971262820741615</v>
+        <v>0.9970343180928367</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.8642549388007055</v>
+        <v>0.9879515598289501</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.5786030767448622</v>
+        <v>0.7272926245226898</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.3389026987179165</v>
+        <v>-0.1669039391512541</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.2636</t>
+          <t>X &gt; 0.2635</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1273</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.564645634823073</v>
+        <v>1.535449840470442</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.859979573181086</v>
+        <v>2.85879278673643</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.386653592982213</v>
+        <v>2.386500202977892</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.438324141126735</v>
+        <v>2.437829648748732</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.821479992587207</v>
+        <v>1.870025912352979</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.433072403997627</v>
+        <v>2.457029812947241</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.112698258399959</v>
+        <v>2.16070993739028</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.274066378163887</v>
+        <v>2.323313940557604</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.820311244421944</v>
+        <v>1.893568354201641</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.441720020755085</v>
+        <v>1.541067346049658</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.101119412377059</v>
+        <v>2.201027448395735</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.742724587513223</v>
+        <v>1.866421208541468</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.558237520531314</v>
+        <v>1.706927068309142</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.5270996436565127</v>
+        <v>0.6990984032231751</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.3221</t>
+          <t>X &gt; 0.322</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1064</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.74840727773632</v>
+        <v>1.719211483383688</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.486845244822867</v>
+        <v>2.485658458378211</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.186058822473846</v>
+        <v>2.185905432469525</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.692223815686269</v>
+        <v>2.691729323308266</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.965964337778551</v>
+        <v>2.014510257544323</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.263338367413638</v>
+        <v>2.287295776363251</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.084643045741451</v>
+        <v>2.132654724731772</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.899529289172754</v>
+        <v>1.948776851566471</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.180652395807876</v>
+        <v>1.253909505587572</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.5187035242900393</v>
+        <v>0.6180508495846126</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.159867027683987</v>
+        <v>1.259775063702662</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.7243203680092378</v>
+        <v>0.8480169890374825</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.3981544771018406</v>
+        <v>0.5468440248796682</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.3159594967317787</v>
+        <v>-0.1439607371651164</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.3807</t>
+          <t>X &gt; 0.3805</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>870</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.427129946477145</v>
+        <v>1.397934152124513</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.999851899390329</v>
+        <v>1.998665112945673</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.145310399692754</v>
+        <v>1.145157009688432</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.424960830637438</v>
+        <v>2.424466338259435</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.31195863386359</v>
+        <v>1.360504553629362</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.724275192234302</v>
+        <v>1.748232601183915</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.94990966055434</v>
+        <v>0.9979213395446607</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4828410167676012</v>
+        <v>0.5320885791613179</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1528537834333292</v>
+        <v>-0.07959667365363288</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.8878300510275636</v>
+        <v>-0.7884827257329903</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2867791355398381</v>
+        <v>0.3866871715585134</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3684978845186393</v>
+        <v>-0.2448012634903947</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.5587636803607765</v>
+        <v>-0.4100741325829489</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.252568260019309</v>
+        <v>-1.080569500452647</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.4392</t>
+          <t>X &gt; 0.439</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>737</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.335908935544339</v>
+        <v>2.306713141191707</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.217260155913351</v>
+        <v>2.216073369468695</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.008377509285857</v>
+        <v>1.008224119281536</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.495454755994977</v>
+        <v>2.494960263616974</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.278739151338904</v>
+        <v>1.327285071104676</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.304742760349839</v>
+        <v>1.328700169299452</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.491402821707823</v>
+        <v>1.539414500698143</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.4815933366727805</v>
+        <v>0.5308408990664972</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2849259698379285</v>
+        <v>0.3581830796176249</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5649928264919311</v>
+        <v>-0.4656455011973577</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.7228433286807103</v>
+        <v>0.8227513646993856</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.3282602014605729</v>
+        <v>-0.2045635804323283</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.06570020709847313</v>
+        <v>0.2143897548763007</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.065416245795753</v>
+        <v>-0.8934174862290902</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.4977</t>
+          <t>X &gt; 0.4975</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>624</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.44857114895283</v>
+        <v>3.419375354600199</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.600205568709505</v>
+        <v>3.599018782264849</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.442613671133962</v>
+        <v>1.442460281129641</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.175402917286419</v>
+        <v>3.174908424908416</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.637113364190725</v>
+        <v>2.685659283956497</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.453718163056585</v>
+        <v>2.477675572006198</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.689520624303235</v>
+        <v>2.737532303293555</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.222451980516496</v>
+        <v>2.271699542910213</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.321726234250129</v>
+        <v>2.394983344029825</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.31155102766386</v>
+        <v>1.410898352958434</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.549157561711368</v>
+        <v>2.649065597730043</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.3014844320154</v>
+        <v>1.425181053043644</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.842872040240458</v>
+        <v>1.991561588018286</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.6262999981592969</v>
+        <v>0.7982987577259593</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.5563</t>
+          <t>X &gt; 0.5561</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.882720333102007</v>
+        <v>3.751231187817197</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.907897876401812</v>
+        <v>3.982936135329219</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.69494467346496</v>
+        <v>1.592827911079851</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.097897089780602</v>
+        <v>3.17461757842883</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.10506208213944</v>
+        <v>3.229833047277275</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.402436111774527</v>
+        <v>3.502618566096203</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.681362116144726</v>
+        <v>3.62345068013753</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.577929835994354</v>
+        <v>3.52059432628775</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3.698765861289765</v>
+        <v>3.665109920417741</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.030665246778085</v>
+        <v>3.022769542869554</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.462327724881526</v>
+        <v>4.452022924734557</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.223978604509583</v>
+        <v>3.239772239231932</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.531100478468893</v>
+        <v>3.570567125735259</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.302290674149972</v>
+        <v>2.367706361616314</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.6148</t>
+          <t>X &gt; 0.6146</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>496</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.164245259788224</v>
+        <v>3.135049465435593</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.367575295756659</v>
+        <v>3.366388509312003</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.158287781969356</v>
+        <v>1.158134391965035</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.103029054589982</v>
+        <v>3.102534562211979</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.766352404720095</v>
+        <v>2.814898324485867</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.466952240806798</v>
+        <v>3.490909649756411</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.382241881540629</v>
+        <v>3.43025356053095</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.116786140979691</v>
+        <v>3.166033703373408</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.055803984456915</v>
+        <v>3.129061094236611</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.407498091352863</v>
+        <v>2.506845416647437</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.218925965350735</v>
+        <v>4.31883400136941</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.245239601577019</v>
+        <v>3.368936222605264</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.833153264392649</v>
+        <v>3.981842812170477</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.445985688812733</v>
+        <v>2.617984448379396</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.6733</t>
+          <t>X &gt; 0.6731</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>431</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.435557287331079</v>
+        <v>3.406361492978448</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.520426878722006</v>
+        <v>2.51924009227735</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.893636932482046</v>
+        <v>1.893483542477725</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.880010567949753</v>
+        <v>3.87951607557175</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.645665330399304</v>
+        <v>2.694211250165075</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.407076483004232</v>
+        <v>3.431033891953845</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.554384685222978</v>
+        <v>3.602396364213298</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.855297479951325</v>
+        <v>2.904545042345042</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.258352446398391</v>
+        <v>3.331609556178087</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.944396527098689</v>
+        <v>2.043743852393263</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.131806737748008</v>
+        <v>3.231714773766683</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.310036398223978</v>
+        <v>1.433733019252223</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.514015475305008</v>
+        <v>2.662705023082836</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.115621195137102</v>
+        <v>1.287619954703764</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.7318</t>
+          <t>X &gt; 0.7316</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>387</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.36662918910389</v>
+        <v>4.337433394751258</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.78903482730621</v>
+        <v>3.787848040861554</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.91105930818425</v>
+        <v>3.910905918179928</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.333274115855289</v>
+        <v>5.332779623477286</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.502994898676917</v>
+        <v>3.551540818442689</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.800368928312004</v>
+        <v>3.824326337261617</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.715658569045836</v>
+        <v>3.763670248036156</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.731794059626019</v>
+        <v>2.781041622019735</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.446005701552856</v>
+        <v>3.519262811332553</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.820893106773383</v>
+        <v>1.920240432067956</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.391385746962804</v>
+        <v>2.491293782981479</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.1582154288472495</v>
+        <v>-0.03451880781900485</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.4552254491054981</v>
+        <v>0.6039149968833257</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.6110285647506615</v>
+        <v>-0.4390298051839991</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.7904</t>
+          <t>X &gt; 0.7901</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>348</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.415635693603583</v>
+        <v>4.386439899250952</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.241231209735155</v>
+        <v>4.240044423290499</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.133816146819186</v>
+        <v>4.133662756814864</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.413466577763884</v>
+        <v>5.412972085385881</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.151039093633699</v>
+        <v>3.199585013399471</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.597838410625108</v>
+        <v>4.621795819574722</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.800484373198024</v>
+        <v>4.848496052188345</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.758703085733117</v>
+        <v>3.807950648126834</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.559789894727594</v>
+        <v>4.63304700450729</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.135158454719566</v>
+        <v>3.234505780014139</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.505169940137542</v>
+        <v>3.605077976156217</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.240697517780212</v>
+        <v>1.364394138808457</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.682615629984049</v>
+        <v>1.831305177761877</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.1031429726629867</v>
+        <v>0.06885578690367566</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.8489</t>
+          <t>X &gt; 0.8486</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.929340379722056</v>
+        <v>4.03940894188618</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.561744030247972</v>
+        <v>4.373164764078574</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.128511107031393</v>
+        <v>4.937893229437982</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.540787532671033</v>
+        <v>6.345732542218158</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.399933877011243</v>
+        <v>4.259039311809374</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.017820727159148</v>
+        <v>4.851313648519671</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4.292084726867344</v>
+        <v>4.151679923511466</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.504503262567781</v>
+        <v>3.366358345236755</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.405059567583464</v>
+        <v>4.287852189774071</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.555140771253605</v>
+        <v>3.464023608959089</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.029926792480595</v>
+        <v>2.940394343531629</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.78225366278464</v>
+        <v>1.720605809331019</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.362102809471232</v>
+        <v>1.644936700658576</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.3057871776464722</v>
+        <v>0.6160262911084402</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.9074</t>
+          <t>X &gt; 0.9071</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>279</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.225177159429805</v>
+        <v>5.195981365077174</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.613991066365976</v>
+        <v>3.61280427992132</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.65291143788334</v>
+        <v>4.652758047879018</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.141559520539793</v>
+        <v>5.14106502816179</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.452732333035499</v>
+        <v>2.501278252801271</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.825375179874889</v>
+        <v>3.849332588824502</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.023818942472523</v>
+        <v>3.071830621462844</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.915173237753891</v>
+        <v>2.964420800147607</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.929459898435411</v>
+        <v>4.002717008215107</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.437964041173643</v>
+        <v>3.537311366468217</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.874839943845359</v>
+        <v>2.974747979864034</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.192372218064477</v>
+        <v>2.316068839092722</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.413798425682977</v>
+        <v>1.562487973460804</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.1525806194309993</v>
+        <v>0.01941814013566301</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.966</t>
+          <t>X &gt; 0.9657</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>240</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.769083969465647</v>
+        <v>3.739888175113016</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.574564543068483</v>
+        <v>2.573377756623827</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.429793158313451</v>
+        <v>3.42963976830913</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.810018301901806</v>
+        <v>4.809523809523803</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.355062082139447</v>
+        <v>1.403608001905219</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.485769445107863</v>
+        <v>2.509726854057476</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.7343924191750375</v>
+        <v>0.7824040981653582</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.683990442054963</v>
+        <v>0.7332380044486797</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.456341618865515</v>
+        <v>1.529598728645212</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.439756155868984</v>
+        <v>1.539103481163558</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.8183883309421276</v>
+        <v>0.9182963669608029</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.01943314996412226</v>
+        <v>0.1431297709923669</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.432615629984042</v>
+        <v>0.5813051777618696</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.008315386456083</v>
+        <v>-0.8363166268894204</v>
       </c>
     </row>
     <row r="30">
@@ -3462,49 +3462,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.074639525021205</v>
+        <v>2.989888175113023</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.473554442058379</v>
+        <v>2.406711089957156</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.088884067404358</v>
+        <v>3.012973101642451</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.724159716043218</v>
+        <v>3.142857142857132</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.359584382507016</v>
+        <v>-1.346391998094781</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.4529411622795863</v>
+        <v>-0.07360647927584552</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.651971217188603</v>
+        <v>-2.134262568501313</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.119039860975342</v>
+        <v>-2.600095328884656</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6648705023466093</v>
+        <v>-1.137067938021453</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.514789298676469</v>
+        <v>-1.960896518836435</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.214439951886149</v>
+        <v>-1.665036966372519</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.685112304581338</v>
+        <v>-2.106870229007633</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.610313662945245</v>
+        <v>-3.002028155571459</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.394679022819723</v>
+        <v>-3.752983293556092</v>
       </c>
     </row>
     <row r="31">
@@ -3517,98 +3517,98 @@
         <v>175</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.804798255179932</v>
+        <v>1.775602460827301</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.907897876401826</v>
+        <v>1.90671108995717</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.513126491646787</v>
+        <v>1.512973101642466</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.929065920949427</v>
+        <v>3.928571428571423</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.180652203574837</v>
+        <v>-1.132106283809065</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.45470674536832</v>
+        <v>-1.430749336418707</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.25370281892021</v>
+        <v>-3.20569113992989</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-3.720771462706949</v>
+        <v>-3.671523900313233</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.63889647637258</v>
+        <v>-2.565639366592883</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.917386701273863</v>
+        <v>-2.818039375979289</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-3.122087859534055</v>
+        <v>-3.02217982351538</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-4.230566850035878</v>
+        <v>-4.106870229007633</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-4.650717703349287</v>
+        <v>-4.502028155571459</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-6.139267767408462</v>
+        <v>-5.9672690078418</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 1.142</t>
+          <t>X &gt; 1.141</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>145</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.06712292708607492</v>
+        <v>-0.09631872143870623</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.9886538477361171</v>
+        <v>-0.9898406341807728</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-3.45239074973253</v>
+        <v>-3.452544139736851</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.253200088902794</v>
+        <v>-1.253694581280797</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-6.619075848895037</v>
+        <v>-6.570529929129265</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-7.011356991673743</v>
+        <v>-6.98739958272413</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-8.475377695767499</v>
+        <v>-8.427366016777178</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-8.942446339554238</v>
+        <v>-8.893198777160521</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7.624118151249426</v>
+        <v>-7.55086104146973</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-10.54300246482066</v>
+        <v>-10.44365513952609</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-10.05804845066707</v>
+        <v>-9.958140414648391</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-10.02367029831174</v>
+        <v>-9.899973677283498</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-9.754165979211358</v>
+        <v>-9.60547643143353</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-11.5973958462262</v>
+        <v>-11.42539708665954</v>
       </c>
     </row>
     <row r="33">
@@ -3621,98 +3621,98 @@
         <v>111</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.129564679183005</v>
+        <v>-1.158760473535636</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.740750772246834</v>
+        <v>-2.74193755869149</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.937323958803674</v>
+        <v>-4.937477348807995</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.203495211611703</v>
+        <v>-1.203989703989706</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-11.65169467461731</v>
+        <v>-11.60314875485154</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-10.45341974408132</v>
+        <v>-10.42946233513171</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-13.24083280605019</v>
+        <v>-13.19282112705987</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-13.70790144983693</v>
+        <v>-13.65865388744322</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-12.86798270545881</v>
+        <v>-12.79472559567911</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-14.61880240268957</v>
+        <v>-14.51945507739499</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-13.02170175914796</v>
+        <v>-12.92179372312928</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-17.49182811129714</v>
+        <v>-17.36813149026889</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-17.91197896461055</v>
+        <v>-17.76328941683272</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-19.48804511618582</v>
+        <v>-19.31604635661915</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 1.259</t>
+          <t>X &gt; 1.258</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>98</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.460507867269044</v>
+        <v>-1.489703661621675</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.051285797067564</v>
+        <v>-2.05247258351222</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.425649018557301</v>
+        <v>-1.425802408561623</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.29542387496894</v>
+        <v>-1.295918367346943</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-9.996978734187081</v>
+        <v>-9.948432814421309</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.679196541286686</v>
+        <v>-8.655239132337073</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-11.82513139034878</v>
+        <v>-11.77711971135846</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-11.27179187087021</v>
+        <v>-11.22254430847649</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-14.3939985171889</v>
+        <v>-14.32074140740921</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-16.26432547678407</v>
+        <v>-16.1649781514895</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-15.44861847177896</v>
+        <v>-15.34871043576028</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-21.53668929901547</v>
+        <v>-21.41299267798723</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-22.97724831559419</v>
+        <v>-22.82855876781636</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-25.81273715516357</v>
+        <v>-25.64073839559691</v>
       </c>
     </row>
     <row r="35">
@@ -3722,49 +3722,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-3.730916030534353</v>
+        <v>-3.127395775504269</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-2.842102123598188</v>
+        <v>-2.241437058190989</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.7368735083532201</v>
+        <v>-0.1660392440365541</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.6433516352351489</v>
+        <v>-0.0361552028218739</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-6.144937917860553</v>
+        <v>-6.698243849946635</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-7.097563888225466</v>
+        <v>-7.660026232362277</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-10.93227424749163</v>
+        <v>-11.42438602529144</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-12.64934289127837</v>
+        <v>-13.12478668690935</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-11.46032504780115</v>
+        <v>-11.92719139481158</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-14.81024384413101</v>
+        <v>-15.22015577809569</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-13.7649450023912</v>
+        <v>-14.18972832439722</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-19.98056685003588</v>
+        <v>-20.30440109320516</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-24.15071770334929</v>
+        <v>-24.40326272347269</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-26.42498205312275</v>
+        <v>-26.62335366392647</v>
       </c>
     </row>
   </sheetData>
@@ -3908,49 +3908,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.01908396946565</v>
+        <v>10.45285113807598</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.407897876401819</v>
+        <v>8.869674052920125</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.01312649164678</v>
+        <v>8.47593606460542</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>13.14335163523514</v>
+        <v>13.54409171075838</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12.60506208213945</v>
+        <v>13.05484256980646</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.40243611177453</v>
+        <v>10.85849228615625</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.31772575250837</v>
+        <v>10.79783619693079</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.60065710872162</v>
+        <v>9.097435535312876</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.789674952198851</v>
+        <v>9.060462926176079</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>15.18975615586899</v>
+        <v>14.40947385153393</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>17.4850549976088</v>
+        <v>16.67446920646698</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>15.01943314996412</v>
+        <v>15.4980680425973</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>17.09928229665071</v>
+        <v>17.57204591850262</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>17.32501794687725</v>
+        <v>17.82109078051798</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>225</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.185750636132312</v>
+        <v>2.15655484177968</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.092102123598181</v>
+        <v>-2.093288910042837</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.931317952797663</v>
+        <v>-2.931471342801984</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.023315031431522</v>
+        <v>-1.023809523809526</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2.450493473416103</v>
+        <v>-2.401947553650331</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.26423055489213</v>
+        <v>-1.240273145942517</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.126718691936077</v>
+        <v>-3.078707012945756</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.704898446833923</v>
+        <v>-2.655650884440206</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.321436158912263</v>
+        <v>-2.248179049132567</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5046882885754513</v>
+        <v>-0.405340963280878</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.7093894468356439</v>
+        <v>-0.6094814108169686</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-2.452789072258099</v>
+        <v>-2.329092451229855</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.984051036682622</v>
+        <v>-1.835361488904795</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.4249820531227471</v>
+        <v>-0.2529832935560847</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>385</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.27312382274215</v>
+        <v>-0.3023196170947813</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.481712513208571</v>
+        <v>-4.482899299653226</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.798561820041535</v>
+        <v>-2.798715210045856</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.408596416712918</v>
+        <v>-2.409090909090921</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.466366489289129</v>
+        <v>-3.417820569523357</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.90925219991378</v>
+        <v>-2.885294790964167</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.032923598140989</v>
+        <v>-3.984911919150669</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.720771462706949</v>
+        <v>-3.671523900313233</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.742792580268684</v>
+        <v>-2.669535470488988</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.255049038936207</v>
+        <v>-1.155701713641633</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.200009937456137</v>
+        <v>-1.100101901437462</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.425372044841076</v>
+        <v>-1.301675423812831</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.105263157894747</v>
+        <v>-1.956573610116919</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.06134568948639441</v>
+        <v>0.1106530700802679</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>579</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3688249021081305</v>
+        <v>0.4008470792226007</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.587784334306292</v>
+        <v>-1.5247957593579</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.291709432360122</v>
+        <v>-1.233602240823302</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.565631427981252</v>
+        <v>0.7798434442269979</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.2000534465608652</v>
+        <v>0.2905943032750784</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.4974274761959521</v>
+        <v>0.8294809992833265</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1054175980961247</v>
+        <v>0.2542451501950893</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.3997746702075631</v>
+        <v>-0.1172774594688448</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.611782033373288</v>
+        <v>1.833672165248771</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.488978953796448</v>
+        <v>2.659793136335971</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.802412510562164</v>
+        <v>2.902320546580839</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.354925377943395</v>
+        <v>3.47862199897164</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.934774524629987</v>
+        <v>3.083464072407814</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.851356461557728</v>
+        <v>3.85064364944909</v>
       </c>
     </row>
     <row r="10">
@@ -4116,257 +4116,257 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>841</v>
+        <v>851</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.8982665580841811</v>
+        <v>-0.7740007137758695</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.096796959278933</v>
+        <v>-2.065478944805285</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.960434025392004</v>
+        <v>-1.934822722023434</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1139398705292578</v>
+        <v>0.1144018583042907</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.7135480474247515</v>
+        <v>-0.892903626001754</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.059828039168863</v>
+        <v>-1.139380635271195</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.671648509593169</v>
+        <v>-1.837059771298513</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.8940237423422062</v>
+        <v>-1.074424383727134</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.292633532080508</v>
+        <v>0.003118977866392925</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2711171026145465</v>
+        <v>-0.05446377029841898</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.081026561589844</v>
+        <v>0.7436281390138859</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3530630432025532</v>
+        <v>-0.06935557484585075</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.0001136505699506074</v>
+        <v>-0.5161126626137076</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.2932105747012628</v>
+        <v>-0.3187882289262447</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.08758</t>
+          <t>X &lt; -0.08761</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.8943339815769704</v>
+        <v>-0.8045462952640108</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.549452395830485</v>
+        <v>-2.520961866017679</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.352450256763753</v>
+        <v>-2.32875351706258</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.8111938193103185</v>
+        <v>-0.801787321589309</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.482745015221788</v>
+        <v>-1.603148754851539</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.501024726112533</v>
+        <v>-1.552867074406599</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.810806608476135</v>
+        <v>-1.926681341064487</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.773430482519252</v>
+        <v>-1.893229926897298</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.9637497053353954</v>
+        <v>-1.158767757189622</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.398452253637409</v>
+        <v>-1.662253984899785</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.187177390314346</v>
+        <v>-1.454892038836292</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.018112637581666</v>
+        <v>-2.344404227194396</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.663549967327285</v>
+        <v>-3.053752293502498</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.204798566884229</v>
+        <v>-2.665335700458904</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.02905</t>
+          <t>X &lt; -0.02909</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1371</v>
+        <v>1382</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.541609672152852</v>
+        <v>-1.470685301589491</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.609817235673383</v>
+        <v>-2.586832669009844</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.460824304301127</v>
+        <v>-2.441082892614538</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.858458647168916</v>
+        <v>-1.842775041050906</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.634068352643155</v>
+        <v>-1.719145412904268</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.805685715636628</v>
+        <v>-1.839793529635564</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.360068151700631</v>
+        <v>-2.438438234448036</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.861761191931961</v>
+        <v>-2.938712043582058</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.721952954777898</v>
+        <v>-1.856606510479992</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.951152935040099</v>
+        <v>-2.13694269488262</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.043693182886109</v>
+        <v>-2.23001891583101</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.552489646831212</v>
+        <v>-2.78317080704231</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.006402834544623</v>
+        <v>-3.284385350076157</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.66859985035105</v>
+        <v>-2.996832787043793</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.02948</t>
+          <t>X &lt; 0.02942</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1562</v>
+        <v>1573</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.004725554343878</v>
+        <v>-1.942646503323296</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.694389290053074</v>
+        <v>-2.673730550421382</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.230039433337332</v>
+        <v>-2.214299625630268</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.621279408021856</v>
+        <v>-1.609195920945766</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.680424868847183</v>
+        <v>-1.74904686535141</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.240875990136296</v>
+        <v>-2.264941077631327</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.929565515815412</v>
+        <v>-2.988692948248151</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.491179625972251</v>
+        <v>-3.5484803827162</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.817217198407398</v>
+        <v>-2.919070472875703</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.931252784105467</v>
+        <v>-3.075671407866231</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.974210178110049</v>
+        <v>-3.119351687184711</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.609083474076797</v>
+        <v>-3.789409911547317</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.867608298358881</v>
+        <v>-4.087796897629914</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.736121617783439</v>
+        <v>-3.996149218540204</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 0.08801</t>
+          <t>X &lt; 0.08794</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1771</v>
+        <v>1782</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.032485537260811</v>
+        <v>-1.98086391402348</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.325416761848317</v>
+        <v>-2.309565387188883</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.568803923616969</v>
+        <v>-1.558973356807059</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.352717988571705</v>
+        <v>-1.34375</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.130892974040329</v>
+        <v>-1.189217235392384</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.590256412115288</v>
+        <v>-1.612712624527248</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.207583583824587</v>
+        <v>-2.258633725572302</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.870220775352657</v>
+        <v>-2.918887275193384</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.282397119873217</v>
+        <v>-2.367062342050552</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.539117083567632</v>
+        <v>-2.657425074267564</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.713648497317926</v>
+        <v>-2.83170363303919</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.931074464249072</v>
+        <v>-3.079964399411217</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.321146597254476</v>
+        <v>-3.501467303075664</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.121763532512922</v>
+        <v>-3.33491370881984</v>
       </c>
     </row>
     <row r="15">
@@ -4376,777 +4376,777 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2152</v>
+        <v>2162</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.025950672566687</v>
+        <v>-1.015858951323764</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.689144637461403</v>
+        <v>-1.701384586215795</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.7651906604567884</v>
+        <v>-0.7824709848738749</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5176104369202648</v>
+        <v>-0.5357800578795135</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.1054885888461996</v>
+        <v>-0.1711271431892101</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4308972215588014</v>
+        <v>-0.4722239907965857</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.3515655860743081</v>
+        <v>-0.4157286819176349</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.7007794065703052</v>
+        <v>-0.7643019709510739</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1338299156731892</v>
+        <v>-0.2224394193320194</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.03055924301783364</v>
+        <v>-0.1437220036009776</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.02364569844688447</v>
+        <v>-0.1373233405064767</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.08326787605511754</v>
+        <v>-0.05326579277842569</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.06084755443055201</v>
+        <v>-0.09888437378690185</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.4523413669516003</v>
+        <v>0.2687558368786895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.2051</t>
+          <t>X &lt; 0.205</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2493</v>
+        <v>2504</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.08666223963251696</v>
+        <v>-0.06672684276540508</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.7587687902648454</v>
+        <v>-0.7546561596453856</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5331993869474729</v>
+        <v>-0.5307644729102208</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5012748130269387</v>
+        <v>-0.4987498579384066</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2586469506343363</v>
+        <v>-0.2900847955480188</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.018995315654493</v>
+        <v>-1.03061284870261</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.8022742474916384</v>
+        <v>-0.8309969372786981</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.287798273431235</v>
+        <v>-1.315234771115733</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.7667702039260504</v>
+        <v>-0.8126358933821507</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.5536359146155903</v>
+        <v>-0.6179938075126756</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.7360988485450477</v>
+        <v>-0.800058904944521</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.5592241646651388</v>
+        <v>-0.6399907397817728</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.2353207506628365</v>
+        <v>-0.3343634849127781</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.2537183078880716</v>
+        <v>0.1367930642713873</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.2636</t>
+          <t>X &lt; 0.2635</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2707</v>
+        <v>2718</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.5691513246519975</v>
+        <v>-0.5511224437079321</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.241789508666223</v>
+        <v>-1.236146052899976</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.9180729196850805</v>
+        <v>-0.9142896319595906</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7681316183533724</v>
+        <v>-0.7647674905739521</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.6975888751506858</v>
+        <v>-0.7209794568406522</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.006403667230991</v>
+        <v>-1.015279259906812</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.071367836290456</v>
+        <v>-1.092978164831592</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.408097037979438</v>
+        <v>-1.42902337587438</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.006785224792296</v>
+        <v>-1.042319498799998</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.8776543937436969</v>
+        <v>-0.9278325952508339</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.172694079881978</v>
+        <v>-1.222001317713946</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.8595812464921337</v>
+        <v>-0.9230466995958651</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.6315153399814832</v>
+        <v>-0.7094573574839202</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2003791717042134</v>
+        <v>-0.2927183928938462</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.3221</t>
+          <t>X &lt; 0.322</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2916</v>
+        <v>2927</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4836473381478754</v>
+        <v>-0.4692954983563666</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.8134135990080154</v>
+        <v>-0.8098591720367097</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.6091830402971894</v>
+        <v>-0.6068362925032105</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6314262184900841</v>
+        <v>-0.6288486794104813</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.5701515930742289</v>
+        <v>-0.588898810083883</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6987950783759516</v>
+        <v>-0.7064855252724414</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.8334887531365212</v>
+        <v>-0.8510314846567297</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.008343575741065</v>
+        <v>-1.025768700858741</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.5715027266782471</v>
+        <v>-0.6009151412956655</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3753123372816987</v>
+        <v>-0.4167136460967598</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.5951950880369736</v>
+        <v>-0.6360267274646745</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.301848549830261</v>
+        <v>-0.3540535680311905</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.05147190286933778</v>
+        <v>-0.1154161337135378</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1593800867949469</v>
+        <v>0.08456368287028937</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.3807</t>
+          <t>X &lt; 0.3805</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3110</v>
+        <v>3121</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.2554917590005701</v>
+        <v>-0.2446363941275749</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.472627427890302</v>
+        <v>-0.4705630881468892</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1453163151459194</v>
+        <v>-0.1447535905669994</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.3502381083546027</v>
+        <v>-0.3488388009307855</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.2299812009641116</v>
+        <v>-0.2457530204589986</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3640808863011529</v>
+        <v>-0.3709858337021927</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3351455981493174</v>
+        <v>-0.3503751004706217</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.4317562417276619</v>
+        <v>-0.4470732630068142</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.08993981505636839</v>
+        <v>-0.1146751037284304</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.07334639350546723</v>
+        <v>0.03910348116357198</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.2418161877429554</v>
+        <v>-0.2751522032483251</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.06763366410294225</v>
+        <v>0.02505420262861691</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2441713998329718</v>
+        <v>0.1923984940121386</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.3917382041119808</v>
+        <v>0.3314447743708584</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.4392</t>
+          <t>X &lt; 0.439</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3243</v>
+        <v>3254</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.3924639420822658</v>
+        <v>-0.3827778793712184</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4208271620006414</v>
+        <v>-0.4190696816288693</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.06155082857448946</v>
+        <v>-0.06129948641267191</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.2527442762311978</v>
+        <v>-0.2517507002801196</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1593905623869958</v>
+        <v>-0.1727787587444851</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.183537434826512</v>
+        <v>-0.1897928679944343</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.405351170568558</v>
+        <v>-0.4177645617549217</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3940335653319309</v>
+        <v>-0.4068437951423292</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.191852141397213</v>
+        <v>-0.2122443725105612</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.03930143575404799</v>
+        <v>-0.06771051515319471</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3191655815655636</v>
+        <v>-0.3467993243706786</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.04061959064208764</v>
+        <v>0.004923382785982255</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.06938094030053321</v>
+        <v>0.02638966316893487</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2817709533527335</v>
+        <v>0.2313436886196882</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.4977</t>
+          <t>X &lt; 0.4975</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3356</v>
+        <v>3367</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.5070365410716065</v>
+        <v>-0.4982775053603561</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5885391782300147</v>
+        <v>-0.5863341897113798</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.1061191275988378</v>
+        <v>-0.1057361937986272</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2865354711225478</v>
+        <v>-0.2854816193578458</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.3629914096881919</v>
+        <v>-0.3736431829289089</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.3466720927438942</v>
+        <v>-0.3513842570536241</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.5639275332483962</v>
+        <v>-0.5738002092837675</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.6877129091248904</v>
+        <v>-0.6974863754307563</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5539727716928482</v>
+        <v>-0.5700453994686612</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.4054819393691034</v>
+        <v>-0.4284135760894685</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6233850142995081</v>
+        <v>-0.645749132544637</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2746407035200917</v>
+        <v>-0.3039613539705286</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.2610841019194439</v>
+        <v>-0.2965649726735933</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.07814057517281725</v>
+        <v>-0.1199271604999552</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.5563</t>
+          <t>X &lt; 0.5561</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3430</v>
+        <v>3440</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.4913720282108045</v>
+        <v>-0.4684089578148658</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.5476512229590185</v>
+        <v>-0.5591058277716883</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1131449410762642</v>
+        <v>-0.09699502353865341</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1996716205788118</v>
+        <v>-0.2122153209109854</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3732746436529339</v>
+        <v>-0.3958266168248485</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.4381688911341257</v>
+        <v>-0.4552770129185433</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.652597203557967</v>
+        <v>-0.645286647410515</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.8420087818487971</v>
+        <v>-0.8342798906954556</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.7125084539146869</v>
+        <v>-0.7103625679198586</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.6438198487902937</v>
+        <v>-0.6473076686622221</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.861507775475971</v>
+        <v>-0.8644270331747279</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5487486682176979</v>
+        <v>-0.5577708681709126</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4863341417054485</v>
+        <v>-0.500865702796105</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.3316875924813587</v>
+        <v>-0.3518205028584163</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.6148</t>
+          <t>X &lt; 0.6146</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3484</v>
+        <v>3495</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3219226076004134</v>
+        <v>-0.3151289286498127</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4021707734837605</v>
+        <v>-0.4006741395837565</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.009048043403296901</v>
+        <v>-0.008989248614248879</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1494360007121998</v>
+        <v>-0.148868962706338</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.2714051380151474</v>
+        <v>-0.2801819524326774</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3879418950983222</v>
+        <v>-0.3914768760785918</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.5430591228855022</v>
+        <v>-0.5508816433157051</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.7080821462926963</v>
+        <v>-0.7156337464796252</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.5528300635649828</v>
+        <v>-0.5656393665928832</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.4983172386264201</v>
+        <v>-0.5164838294966287</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.7444402705300064</v>
+        <v>-0.7619494878133466</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.4933321971385709</v>
+        <v>-0.5163640808806704</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.4670735139662128</v>
+        <v>-0.4951631670131107</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3113195961767232</v>
+        <v>-0.3445426640854237</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.6733</t>
+          <t>X &lt; 0.6731</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3549</v>
+        <v>3560</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2911350086365445</v>
+        <v>-0.2850908341229257</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2308272008236756</v>
+        <v>-0.2299070511402661</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.07676114880265317</v>
+        <v>-0.07649763484592143</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1841279938741636</v>
+        <v>-0.183473389355747</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2012898009409412</v>
+        <v>-0.2092387338751038</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.310243112290685</v>
+        <v>-0.3135167931772003</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4921730101463027</v>
+        <v>-0.4991350103291765</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6064455635709223</v>
+        <v>-0.6132753625358021</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.5113942655839239</v>
+        <v>-0.5227621876708213</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.3889801233316845</v>
+        <v>-0.405340963280878</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.5217017591479589</v>
+        <v>-0.5377565846717118</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.1900148928407148</v>
+        <v>-0.2113059392827594</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.2281824920816788</v>
+        <v>-0.2537832805363536</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.09925649662796587</v>
+        <v>-0.1293877879381213</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.7318</t>
+          <t>X &lt; 0.7316</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3593</v>
+        <v>3604</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3455860249880445</v>
+        <v>-0.3398049407288397</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3334336076481108</v>
+        <v>-0.3322269631401795</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.2693374373210276</v>
+        <v>-0.2684930117738631</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2905923003740725</v>
+        <v>-0.2896276385485095</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.2586247585046451</v>
+        <v>-0.2657111234753557</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3070890201332688</v>
+        <v>-0.3100405878029875</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.4600520252694054</v>
+        <v>-0.4664420201767498</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.5508433080608128</v>
+        <v>-0.5571590407960159</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.4854779105026452</v>
+        <v>-0.4958930973453661</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.3471495989266629</v>
+        <v>-0.3622268957765655</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3973143016125533</v>
+        <v>-0.412333889022932</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.01359883890931002</v>
+        <v>-0.03365891453176317</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.02707862386272808</v>
+        <v>0.002826213360577867</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.1015974069384811</v>
+        <v>0.07332081299218629</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.7904</t>
+          <t>X &lt; 0.7901</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3632</v>
+        <v>3643</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2998460716866163</v>
+        <v>-0.2945757198541585</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3324972937408788</v>
+        <v>-0.3313190058020652</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2458633518887652</v>
+        <v>-0.2451002426377755</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2380322197895737</v>
+        <v>-0.2372414062805532</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1846934795194386</v>
+        <v>-0.1914084274485575</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3393221299837137</v>
+        <v>-0.3418891415601593</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5190425904429929</v>
+        <v>-0.5246735274054188</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6138838478479158</v>
+        <v>-0.6194156906275978</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5498906238253483</v>
+        <v>-0.5592170608284732</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4496827880253988</v>
+        <v>-0.4632272015893761</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.4740234067928455</v>
+        <v>-0.4875822214465799</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.1491139056220092</v>
+        <v>-0.1672268819568856</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.08589524257306635</v>
+        <v>-0.1079557077119588</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.04528226405786739</v>
+        <v>0.0193197533832361</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.8489</t>
+          <t>X &lt; 0.8486</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3668</v>
+        <v>3678</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2125107058943101</v>
+        <v>-0.2207593458840051</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3149282105547044</v>
+        <v>-0.2992509696634329</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.2873627717400069</v>
+        <v>-0.2717924174684114</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.2783449389899815</v>
+        <v>-0.2627827703749617</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.2580056361091252</v>
+        <v>-0.2491584749052009</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3266172070502762</v>
+        <v>-0.3142467397207866</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4237708461310845</v>
+        <v>-0.4144525277957527</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.5494517644411445</v>
+        <v>-0.5398347425654393</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.4866659135784488</v>
+        <v>-0.4805379353062804</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4502220576386406</v>
+        <v>-0.4475885340455648</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.394609943824058</v>
+        <v>-0.3921491641448682</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.1815205285099921</v>
+        <v>-0.182957185529375</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.04128734085269059</v>
+        <v>-0.07365087913764512</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.009041938153139029</v>
+        <v>-0.02677339687311786</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.9074</t>
+          <t>X &lt; 0.9071</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3701</v>
+        <v>3712</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2730538872925621</v>
+        <v>-0.2685010866319573</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2003703702989625</v>
+        <v>-0.1996261817936471</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2034683359394265</v>
+        <v>-0.2028474731628052</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.112509318685639</v>
+        <v>-0.1121133031396369</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.07014007419478219</v>
+        <v>-0.07616893977712635</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1893676089048881</v>
+        <v>-0.1918860491683247</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.2863734923675736</v>
+        <v>-0.2916973628008606</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.4690083889854151</v>
+        <v>-0.473952241203115</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.4073029215194381</v>
+        <v>-0.415518301217574</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.4057229264521993</v>
+        <v>-0.417301255112001</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3524180045510263</v>
+        <v>-0.3642294293604138</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.1949200771490283</v>
+        <v>-0.2102627976667577</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.03267340297110621</v>
+        <v>-0.05171843297517853</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.0462419403925054</v>
+        <v>0.02395636161631387</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.966</t>
+          <t>X &lt; 0.9657</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3740</v>
+        <v>3751</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1228025213417041</v>
+        <v>-0.1190384986383108</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.09423431976023267</v>
+        <v>-0.09382040087462684</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.07471675015540313</v>
+        <v>-0.0744803805478611</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.03664836476485789</v>
+        <v>-0.03648345804688091</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.02637443209944479</v>
+        <v>0.0206292785009623</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.06181148694478367</v>
+        <v>-0.06442850641073505</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.1052793182148761</v>
+        <v>-0.1105797584959873</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2908271411448951</v>
+        <v>-0.295730143896634</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2036494803779121</v>
+        <v>-0.2116153288627771</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.2375942714814343</v>
+        <v>-0.2485130301546761</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1869327127839284</v>
+        <v>-0.1980683995105039</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.03067374474458973</v>
+        <v>-0.04505301611128232</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.0453528660171898</v>
+        <v>0.02782259069720538</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.09908211800023281</v>
+        <v>0.07866160113864851</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3782</v>
+        <v>3791</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.04349837572539172</v>
+        <v>-0.03902875443483111</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.05941893962348388</v>
+        <v>-0.05700176831262382</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.01811526949216358</v>
+        <v>-0.01569601987253577</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.07373138207058361</v>
+        <v>0.1022099447513725</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.1828779618545653</v>
+        <v>0.1799237913788971</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.07262080834446039</v>
+        <v>0.09867570024507444</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.02873129486782489</v>
+        <v>0.05241463002422364</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1335033981421532</v>
+        <v>-0.1093131324137531</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.0743334977615433</v>
+        <v>-0.05276867564000298</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.06446994027469088</v>
+        <v>-0.04521799446225572</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.06943641586544658</v>
+        <v>-0.05011867433246664</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.05907374193029824</v>
+        <v>0.07557111030161678</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.2089175068013844</v>
+        <v>0.2226553887323419</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2117181055234596</v>
+        <v>0.2228805946000705</v>
       </c>
     </row>
     <row r="31">
@@ -5208,101 +5208,101 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3805</v>
+        <v>3816</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.03348941734411426</v>
+        <v>0.03624492622296316</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.01822211311874611</v>
+        <v>-0.01805380032497084</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.07287491931973733</v>
+        <v>0.07268044420843722</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.08633983969124159</v>
+        <v>0.08613994473900277</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1653662247718586</v>
+        <v>0.1601439496176411</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1624675830569871</v>
+        <v>0.1596571190505145</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.09212239469094641</v>
+        <v>0.08716039775556084</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.07193538668640542</v>
+        <v>-0.07654744819392079</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.01277206505974959</v>
+        <v>0.005564880612411116</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.008786768783139109</v>
+        <v>-0.01848814187308534</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.01131550181047913</v>
+        <v>0.001498775968400423</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1655455744453391</v>
+        <v>0.1529516672731361</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.2856984816218073</v>
+        <v>0.270306138376661</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.3161480388614706</v>
+        <v>0.298379389882065</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 1.142</t>
+          <t>X &lt; 1.141</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3835</v>
+        <v>3846</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1178365682182445</v>
+        <v>0.1201032567403786</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1059742995887234</v>
+        <v>0.1057779639851546</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2713168192598872</v>
+        <v>0.2705567158503968</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3117521553911899</v>
+        <v>0.3109069353882532</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.3600048500895028</v>
+        <v>0.3546456153941975</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.3595009049049054</v>
+        <v>0.3563364371745834</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.2630667207540682</v>
+        <v>0.2580291522357712</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.09668678849251933</v>
+        <v>0.09201266696166499</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.1802999521988582</v>
+        <v>0.1732410726251317</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2565053092943614</v>
+        <v>0.2468956889557745</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.248864273273206</v>
+        <v>0.2392238806007185</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.3500951254658133</v>
+        <v>0.3380362158988035</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.4400017961293372</v>
+        <v>0.4254477997183841</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.4720192506582137</v>
+        <v>0.4552850371771342</v>
       </c>
     </row>
     <row r="33">
@@ -5312,101 +5312,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3869</v>
+        <v>3880</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1465955614285548</v>
+        <v>0.1485062074788033</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1464961758091903</v>
+        <v>0.1461766603579875</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.2811677287601881</v>
+        <v>0.2803850779981545</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.2966127850160163</v>
+        <v>0.2958134410576534</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.4428650733720474</v>
+        <v>0.4377427409126824</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.3934085131157801</v>
+        <v>0.3903852902714746</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.3228857112286931</v>
+        <v>0.3181428855763784</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.1538829151732415</v>
+        <v>0.1495186700860032</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2620549212231182</v>
+        <v>0.2554674545139406</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2785116425718073</v>
+        <v>0.2697934914622238</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2433194604187179</v>
+        <v>0.2346539942249564</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.4731272858463242</v>
+        <v>0.4619087508996316</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.5844244155137588</v>
+        <v>0.5708911951113578</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.5923350830881589</v>
+        <v>0.5769136136604018</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 1.259</t>
+          <t>X &lt; 1.258</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3882</v>
+        <v>3893</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1506629168340652</v>
+        <v>0.1524585796189086</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1195054778399225</v>
+        <v>0.1192591053220795</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1753407223172161</v>
+        <v>0.1748583475441023</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.293916897311199</v>
+        <v>0.2931261666849636</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.3607804064776658</v>
+        <v>0.356068278686358</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.3124618187154127</v>
+        <v>0.3097567609189724</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2418707769362385</v>
+        <v>0.2375323032935626</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.04613035975042834</v>
+        <v>0.0422488619335013</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.256616037869037</v>
+        <v>0.2503102046157935</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2701730369806725</v>
+        <v>0.2618389186796009</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.2601515227053284</v>
+        <v>0.2518008159683447</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.5150562189651495</v>
+        <v>0.50416956560084</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.6503381812759983</v>
+        <v>0.63716033954924</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.6847551957180542</v>
+        <v>0.669698442893953</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3900</v>
+        <v>3910</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1896691981904084</v>
+        <v>0.1791565921408065</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1256892874447644</v>
+        <v>0.1137483158623169</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1538833313297303</v>
+        <v>0.141894295215522</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.2469321978949921</v>
+        <v>0.2602040816326507</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.2342511330476</v>
+        <v>0.2441923346431665</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2386694792259192</v>
+        <v>0.2502832603872349</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1679945009086765</v>
+        <v>0.1780938266990972</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.02218808670421168</v>
+        <v>0.03269323087019416</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1289835309440477</v>
+        <v>0.1375169917358861</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1641414017706353</v>
+        <v>0.1709379216336728</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1531948899992699</v>
+        <v>0.1600333121861297</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.3814269992721719</v>
+        <v>0.3859723067796921</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.5653807329491016</v>
+        <v>0.5677749638353475</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.5750179468772387</v>
+        <v>0.5756612077226748</v>
       </c>
     </row>
   </sheetData>
